--- a/task2/平安银行.xlsx
+++ b/task2/平安银行.xlsx
@@ -518,10 +518,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>187793</v>
+      </c>
+      <c r="K2" t="n">
         <v>2192480</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2564653480</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -558,10 +558,10 @@
         <v>0.2540220152413155</v>
       </c>
       <c r="J3" t="n">
+        <v>98729</v>
+      </c>
+      <c r="K3" t="n">
         <v>1167960</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1381696680</v>
       </c>
       <c r="L3" t="n">
         <v>0.002540220152413175</v>
@@ -600,10 +600,10 @@
         <v>-1.43581081081081</v>
       </c>
       <c r="J4" t="n">
+        <v>99092</v>
+      </c>
+      <c r="K4" t="n">
         <v>1166803</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1374493934</v>
       </c>
       <c r="L4" t="n">
         <v>-0.01435810810810811</v>
@@ -642,10 +642,10 @@
         <v>0.2570694087403544</v>
       </c>
       <c r="J5" t="n">
+        <v>58321</v>
+      </c>
+      <c r="K5" t="n">
         <v>682353</v>
-      </c>
-      <c r="K5" t="n">
-        <v>799547127.75</v>
       </c>
       <c r="L5" t="n">
         <v>0.002570694087403513</v>
@@ -684,10 +684,10 @@
         <v>0.08547008547009884</v>
       </c>
       <c r="J6" t="n">
+        <v>65977</v>
+      </c>
+      <c r="K6" t="n">
         <v>773255</v>
-      </c>
-      <c r="K6" t="n">
-        <v>905481605</v>
       </c>
       <c r="L6" t="n">
         <v>0.0008547008547010737</v>
@@ -726,10 +726,10 @@
         <v>0.8539709649871873</v>
       </c>
       <c r="J7" t="n">
+        <v>121388</v>
+      </c>
+      <c r="K7" t="n">
         <v>1428132</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1682696529</v>
       </c>
       <c r="L7" t="n">
         <v>0.008539709649871829</v>
@@ -768,10 +768,10 @@
         <v>0.3386960203217539</v>
       </c>
       <c r="J8" t="n">
+        <v>92494</v>
+      </c>
+      <c r="K8" t="n">
         <v>1094667</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1296906728.25</v>
       </c>
       <c r="L8" t="n">
         <v>0.003386960203217493</v>
@@ -810,10 +810,10 @@
         <v>-1.434599156118143</v>
       </c>
       <c r="J9" t="n">
+        <v>111034</v>
+      </c>
+      <c r="K9" t="n">
         <v>1290220</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1498590530</v>
       </c>
       <c r="L9" t="n">
         <v>-0.01434599156118144</v>
@@ -852,10 +852,10 @@
         <v>-0.8561643835616408</v>
       </c>
       <c r="J10" t="n">
+        <v>94196</v>
+      </c>
+      <c r="K10" t="n">
         <v>1095494</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1275155016</v>
       </c>
       <c r="L10" t="n">
         <v>-0.008561643835616417</v>
@@ -894,10 +894,10 @@
         <v>1.813471502590665</v>
       </c>
       <c r="J11" t="n">
+        <v>100551</v>
+      </c>
+      <c r="K11" t="n">
         <v>1174438</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1370569146</v>
       </c>
       <c r="L11" t="n">
         <v>0.01813471502590658</v>
@@ -936,10 +936,10 @@
         <v>-0.254452926208646</v>
       </c>
       <c r="J12" t="n">
+        <v>75586</v>
+      </c>
+      <c r="K12" t="n">
         <v>890027</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1048896819.5</v>
       </c>
       <c r="L12" t="n">
         <v>-0.002544529262086481</v>
@@ -978,10 +978,10 @@
         <v>0.08503401360544036</v>
       </c>
       <c r="J13" t="n">
+        <v>58048</v>
+      </c>
+      <c r="K13" t="n">
         <v>683521</v>
-      </c>
-      <c r="K13" t="n">
-        <v>803478935.5</v>
       </c>
       <c r="L13" t="n">
         <v>0.0008503401360544505</v>
@@ -1020,10 +1020,10 @@
         <v>-0.5947323704333074</v>
       </c>
       <c r="J14" t="n">
+        <v>70950</v>
+      </c>
+      <c r="K14" t="n">
         <v>832247</v>
-      </c>
-      <c r="K14" t="n">
-        <v>975601545.75</v>
       </c>
       <c r="L14" t="n">
         <v>-0.005947323704333041</v>
@@ -1062,10 +1062,10 @@
         <v>1.196581196581201</v>
       </c>
       <c r="J15" t="n">
+        <v>111232</v>
+      </c>
+      <c r="K15" t="n">
         <v>1309198</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1540598746.5</v>
       </c>
       <c r="L15" t="n">
         <v>0.01196581196581192</v>
@@ -1104,10 +1104,10 @@
         <v>0.760135135135134</v>
       </c>
       <c r="J16" t="n">
+        <v>117032</v>
+      </c>
+      <c r="K16" t="n">
         <v>1389170</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1645471865</v>
       </c>
       <c r="L16" t="n">
         <v>0.007601351351351315</v>
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>109822</v>
+      </c>
+      <c r="K17" t="n">
         <v>1308525</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1559761800</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1188,10 +1188,10 @@
         <v>1.089689857502102</v>
       </c>
       <c r="J18" t="n">
+        <v>139651</v>
+      </c>
+      <c r="K18" t="n">
         <v>1675116</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2005951410</v>
       </c>
       <c r="L18" t="n">
         <v>0.01089689857502107</v>
@@ -1230,10 +1230,10 @@
         <v>2.902155887230511</v>
       </c>
       <c r="J19" t="n">
+        <v>177807</v>
+      </c>
+      <c r="K19" t="n">
         <v>2174578</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2661139827.5</v>
       </c>
       <c r="L19" t="n">
         <v>0.02902155887230506</v>
@@ -1272,10 +1272,10 @@
         <v>-1.692183722804197</v>
       </c>
       <c r="J20" t="n">
+        <v>193537</v>
+      </c>
+      <c r="K20" t="n">
         <v>2377600</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2929203200</v>
       </c>
       <c r="L20" t="n">
         <v>-0.01692183722804197</v>
@@ -1314,10 +1314,10 @@
         <v>-1.065573770491795</v>
       </c>
       <c r="J21" t="n">
+        <v>124314</v>
+      </c>
+      <c r="K21" t="n">
         <v>1504820</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1818574970</v>
       </c>
       <c r="L21" t="n">
         <v>-0.0106557377049179</v>
@@ -1356,10 +1356,10 @@
         <v>1.90555095277548</v>
       </c>
       <c r="J22" t="n">
+        <v>111194</v>
+      </c>
+      <c r="K22" t="n">
         <v>1354341</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1650603093.75</v>
       </c>
       <c r="L22" t="n">
         <v>0.0190555095277547</v>
@@ -1398,10 +1398,10 @@
         <v>0.1626016260162567</v>
       </c>
       <c r="J23" t="n">
+        <v>97476</v>
+      </c>
+      <c r="K23" t="n">
         <v>1200412</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1478607481</v>
       </c>
       <c r="L23" t="n">
         <v>0.001626016260162677</v>
@@ -1440,10 +1440,10 @@
         <v>0.2435064935064883</v>
       </c>
       <c r="J24" t="n">
+        <v>64351</v>
+      </c>
+      <c r="K24" t="n">
         <v>794086</v>
-      </c>
-      <c r="K24" t="n">
-        <v>980299167</v>
       </c>
       <c r="L24" t="n">
         <v>0.002435064935064846</v>
@@ -1482,10 +1482,10 @@
         <v>2.024291497975709</v>
       </c>
       <c r="J25" t="n">
+        <v>142311</v>
+      </c>
+      <c r="K25" t="n">
         <v>1775333</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2217834750.25</v>
       </c>
       <c r="L25" t="n">
         <v>0.02024291497975717</v>
@@ -1524,10 +1524,10 @@
         <v>1.428571428571426</v>
       </c>
       <c r="J26" t="n">
+        <v>117841</v>
+      </c>
+      <c r="K26" t="n">
         <v>1495407</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1899166890</v>
       </c>
       <c r="L26" t="n">
         <v>0.01428571428571423</v>
@@ -1566,10 +1566,10 @@
         <v>-0.7042253521126749</v>
       </c>
       <c r="J27" t="n">
+        <v>85769</v>
+      </c>
+      <c r="K27" t="n">
         <v>1090986</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1389097924.5</v>
       </c>
       <c r="L27" t="n">
         <v>-0.007042253521126751</v>
@@ -1608,10 +1608,10 @@
         <v>1.182033096926717</v>
       </c>
       <c r="J28" t="n">
+        <v>94585</v>
+      </c>
+      <c r="K28" t="n">
         <v>1205963</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1539411769.5</v>
       </c>
       <c r="L28" t="n">
         <v>0.01182033096926727</v>
@@ -1650,10 +1650,10 @@
         <v>2.647975077881619</v>
       </c>
       <c r="J29" t="n">
+        <v>190878</v>
+      </c>
+      <c r="K29" t="n">
         <v>2481416</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3233285048</v>
       </c>
       <c r="L29" t="n">
         <v>0.02647975077881615</v>
@@ -1692,10 +1692,10 @@
         <v>-2.048558421851287</v>
       </c>
       <c r="J30" t="n">
+        <v>187260</v>
+      </c>
+      <c r="K30" t="n">
         <v>2443744</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3194584344</v>
       </c>
       <c r="L30" t="n">
         <v>-0.02048558421851288</v>
@@ -1734,10 +1734,10 @@
         <v>0.5422153369481044</v>
       </c>
       <c r="J31" t="n">
+        <v>144905</v>
+      </c>
+      <c r="K31" t="n">
         <v>1872896</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2429146112</v>
       </c>
       <c r="L31" t="n">
         <v>0.005422153369481153</v>
@@ -1776,10 +1776,10 @@
         <v>-1.926040061633282</v>
       </c>
       <c r="J32" t="n">
+        <v>140788</v>
+      </c>
+      <c r="K32" t="n">
         <v>1810531</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2329700764.25</v>
       </c>
       <c r="L32" t="n">
         <v>-0.01926040061633283</v>
@@ -1818,10 +1818,10 @@
         <v>-0.7069913589945001</v>
       </c>
       <c r="J33" t="n">
+        <v>151980</v>
+      </c>
+      <c r="K33" t="n">
         <v>1927864</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2440193858</v>
       </c>
       <c r="L33" t="n">
         <v>-0.007069913589945021</v>
@@ -1860,10 +1860,10 @@
         <v>-0.3955696202531701</v>
       </c>
       <c r="J34" t="n">
+        <v>74972</v>
+      </c>
+      <c r="K34" t="n">
         <v>944641</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1191192301</v>
       </c>
       <c r="L34" t="n">
         <v>-0.003955696202531667</v>
@@ -1902,10 +1902,10 @@
         <v>0.8737092930897493</v>
       </c>
       <c r="J35" t="n">
+        <v>98042</v>
+      </c>
+      <c r="K35" t="n">
         <v>1241206</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1572297700.5</v>
       </c>
       <c r="L35" t="n">
         <v>0.008737092930897417</v>
@@ -1944,10 +1944,10 @@
         <v>-0.7086614173228336</v>
       </c>
       <c r="J36" t="n">
+        <v>85467</v>
+      </c>
+      <c r="K36" t="n">
         <v>1079027</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1362541344.25</v>
       </c>
       <c r="L36" t="n">
         <v>-0.007086614173228312</v>
@@ -1986,10 +1986,10 @@
         <v>-0.951625693893729</v>
       </c>
       <c r="J37" t="n">
+        <v>154263</v>
+      </c>
+      <c r="K37" t="n">
         <v>1935229</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2419520057.25</v>
       </c>
       <c r="L37" t="n">
         <v>-0.009516256938937317</v>
@@ -2028,10 +2028,10 @@
         <v>0.3202562049639643</v>
       </c>
       <c r="J38" t="n">
+        <v>109685</v>
+      </c>
+      <c r="K38" t="n">
         <v>1370520</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1715548410</v>
       </c>
       <c r="L38" t="n">
         <v>0.003202562049639646</v>
@@ -2070,10 +2070,10 @@
         <v>-1.436552274541099</v>
       </c>
       <c r="J39" t="n">
+        <v>157504</v>
+      </c>
+      <c r="K39" t="n">
         <v>1959351</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2436452968.5</v>
       </c>
       <c r="L39" t="n">
         <v>-0.01436552274541103</v>
@@ -2112,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
+        <v>89811</v>
+      </c>
+      <c r="K40" t="n">
         <v>1108267</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1370372145.5</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2154,10 +2154,10 @@
         <v>0.8906882591093216</v>
       </c>
       <c r="J41" t="n">
+        <v>99818</v>
+      </c>
+      <c r="K41" t="n">
         <v>1238243</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1537278684.5</v>
       </c>
       <c r="L41" t="n">
         <v>0.008906882591093179</v>
@@ -2196,10 +2196,10 @@
         <v>-0.9630818619582744</v>
       </c>
       <c r="J42" t="n">
+        <v>81679</v>
+      </c>
+      <c r="K42" t="n">
         <v>1012818</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1257160342.5</v>
       </c>
       <c r="L42" t="n">
         <v>-0.009630818619582704</v>
@@ -2238,10 +2238,10 @@
         <v>1.215559157212321</v>
       </c>
       <c r="J43" t="n">
+        <v>138097</v>
+      </c>
+      <c r="K43" t="n">
         <v>1715164</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2136236762</v>
       </c>
       <c r="L43" t="n">
         <v>0.0121555915721232</v>
@@ -2280,10 +2280,10 @@
         <v>-2.081665332265811</v>
       </c>
       <c r="J44" t="n">
+        <v>136627</v>
+      </c>
+      <c r="K44" t="n">
         <v>1690081</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2091897757.75</v>
       </c>
       <c r="L44" t="n">
         <v>-0.02081665332265814</v>
@@ -2322,10 +2322,10 @@
         <v>0.4088307440719455</v>
       </c>
       <c r="J45" t="n">
+        <v>82560</v>
+      </c>
+      <c r="K45" t="n">
         <v>1012187</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1239929075</v>
       </c>
       <c r="L45" t="n">
         <v>0.004088307440719419</v>
@@ -2364,10 +2364,10 @@
         <v>0.1628664495114117</v>
       </c>
       <c r="J46" t="n">
+        <v>84164</v>
+      </c>
+      <c r="K46" t="n">
         <v>1032690</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1268401492.5</v>
       </c>
       <c r="L46" t="n">
         <v>0.001628664495114007</v>
@@ -2406,10 +2406,10 @@
         <v>1.382113821138211</v>
       </c>
       <c r="J47" t="n">
+        <v>91407</v>
+      </c>
+      <c r="K47" t="n">
         <v>1132078</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1402361622.5</v>
       </c>
       <c r="L47" t="n">
         <v>0.0138211382113822</v>
@@ -2448,10 +2448,10 @@
         <v>-0.08019246190857889</v>
       </c>
       <c r="J48" t="n">
+        <v>55391</v>
+      </c>
+      <c r="K48" t="n">
         <v>690448</v>
-      </c>
-      <c r="K48" t="n">
-        <v>860470820</v>
       </c>
       <c r="L48" t="n">
         <v>-0.000801924619085792</v>
@@ -2490,10 +2490,10 @@
         <v>0.08025682182985383</v>
       </c>
       <c r="J49" t="n">
+        <v>57973</v>
+      </c>
+      <c r="K49" t="n">
         <v>722053</v>
-      </c>
-      <c r="K49" t="n">
-        <v>899497524.75</v>
       </c>
       <c r="L49" t="n">
         <v>0.0008025682182986049</v>
@@ -2532,10 +2532,10 @@
         <v>-0.5613472333600664</v>
       </c>
       <c r="J50" t="n">
+        <v>66704</v>
+      </c>
+      <c r="K50" t="n">
         <v>829796</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1033096020</v>
       </c>
       <c r="L50" t="n">
         <v>-0.005613472333600655</v>
@@ -2574,10 +2574,10 @@
         <v>-0.8064516129032229</v>
       </c>
       <c r="J51" t="n">
+        <v>75656</v>
+      </c>
+      <c r="K51" t="n">
         <v>934353</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1153692366.75</v>
       </c>
       <c r="L51" t="n">
         <v>-0.008064516129032251</v>
@@ -2616,10 +2616,10 @@
         <v>0.243902439024385</v>
       </c>
       <c r="J52" t="n">
+        <v>55222</v>
+      </c>
+      <c r="K52" t="n">
         <v>680056</v>
-      </c>
-      <c r="K52" t="n">
-        <v>838679062</v>
       </c>
       <c r="L52" t="n">
         <v>0.002439024390243905</v>
@@ -2658,10 +2658,10 @@
         <v>-0.5677210056772124</v>
       </c>
       <c r="J53" t="n">
+        <v>90931</v>
+      </c>
+      <c r="K53" t="n">
         <v>1119813</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1379049709.5</v>
       </c>
       <c r="L53" t="n">
         <v>-0.005677210056772131</v>
@@ -2700,10 +2700,10 @@
         <v>-0.4893964110929894</v>
       </c>
       <c r="J54" t="n">
+        <v>101434</v>
+      </c>
+      <c r="K54" t="n">
         <v>1241041</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1520275225</v>
       </c>
       <c r="L54" t="n">
         <v>-0.004893964110929905</v>
@@ -2742,10 +2742,10 @@
         <v>-0.9836065573770428</v>
       </c>
       <c r="J55" t="n">
+        <v>160305</v>
+      </c>
+      <c r="K55" t="n">
         <v>1948503</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2361585636</v>
       </c>
       <c r="L55" t="n">
         <v>-0.009836065573770481</v>
@@ -2784,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>102656</v>
+      </c>
+      <c r="K56" t="n">
         <v>1239058</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1496782064</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2826,10 +2826,10 @@
         <v>-0.1655629139072812</v>
       </c>
       <c r="J57" t="n">
+        <v>73912</v>
+      </c>
+      <c r="K57" t="n">
         <v>892860</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1078128450</v>
       </c>
       <c r="L57" t="n">
         <v>-0.001655629139072801</v>
@@ -2868,10 +2868,10 @@
         <v>0.08291873963515577</v>
       </c>
       <c r="J58" t="n">
+        <v>86924</v>
+      </c>
+      <c r="K58" t="n">
         <v>1048739</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1264517049.25</v>
       </c>
       <c r="L58" t="n">
         <v>0.0008291873963515162</v>
@@ -2910,10 +2910,10 @@
         <v>0.6628003314001663</v>
       </c>
       <c r="J59" t="n">
+        <v>100613</v>
+      </c>
+      <c r="K59" t="n">
         <v>1217418</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1473684489</v>
       </c>
       <c r="L59" t="n">
         <v>0.006628003314001596</v>
@@ -2952,10 +2952,10 @@
         <v>-0.7407407407407396</v>
       </c>
       <c r="J60" t="n">
+        <v>135833</v>
+      </c>
+      <c r="K60" t="n">
         <v>1644260</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1987910340</v>
       </c>
       <c r="L60" t="n">
         <v>-0.007407407407407418</v>
@@ -2994,10 +2994,10 @@
         <v>3.233830845771134</v>
       </c>
       <c r="J61" t="n">
+        <v>247870</v>
+      </c>
+      <c r="K61" t="n">
         <v>3045088</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3745458240</v>
       </c>
       <c r="L61" t="n">
         <v>0.03233830845771135</v>
@@ -3036,10 +3036,10 @@
         <v>-0.7228915662650591</v>
       </c>
       <c r="J62" t="n">
+        <v>111536</v>
+      </c>
+      <c r="K62" t="n">
         <v>1383599</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1716008659.75</v>
       </c>
       <c r="L62" t="n">
         <v>-0.007228915662650603</v>
@@ -3078,10 +3078,10 @@
         <v>-2.427184466019409</v>
       </c>
       <c r="J63" t="n">
+        <v>152588</v>
+      </c>
+      <c r="K63" t="n">
         <v>1860050</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2268795987.5</v>
       </c>
       <c r="L63" t="n">
         <v>-0.02427184466019405</v>
@@ -3120,10 +3120,10 @@
         <v>0.1658374792703115</v>
       </c>
       <c r="J64" t="n">
+        <v>136830</v>
+      </c>
+      <c r="K64" t="n">
         <v>1653588</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1995880716</v>
       </c>
       <c r="L64" t="n">
         <v>0.001658374792703032</v>
@@ -3162,10 +3162,10 @@
         <v>-0.2483443708609219</v>
       </c>
       <c r="J65" t="n">
+        <v>149803</v>
+      </c>
+      <c r="K65" t="n">
         <v>1805126</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2181946052.5</v>
       </c>
       <c r="L65" t="n">
         <v>-0.002483443708609201</v>
@@ -3204,10 +3204,10 @@
         <v>-1.32780082987552</v>
       </c>
       <c r="J66" t="n">
+        <v>155260</v>
+      </c>
+      <c r="K66" t="n">
         <v>1858459</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2222716964</v>
       </c>
       <c r="L66" t="n">
         <v>-0.01327800829875525</v>
@@ -3246,10 +3246,10 @@
         <v>0.7569386038687961</v>
       </c>
       <c r="J67" t="n">
+        <v>125280</v>
+      </c>
+      <c r="K67" t="n">
         <v>1492716</v>
-      </c>
-      <c r="K67" t="n">
-        <v>1778571114</v>
       </c>
       <c r="L67" t="n">
         <v>0.007569386038688064</v>
@@ -3288,10 +3288,10 @@
         <v>-1.919866444073459</v>
       </c>
       <c r="J68" t="n">
+        <v>115232</v>
+      </c>
+      <c r="K68" t="n">
         <v>1367232</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1622904384</v>
       </c>
       <c r="L68" t="n">
         <v>-0.01919866444073459</v>
@@ -3330,10 +3330,10 @@
         <v>-0.0851063829787216</v>
       </c>
       <c r="J69" t="n">
+        <v>110238</v>
+      </c>
+      <c r="K69" t="n">
         <v>1295300</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1517767775</v>
       </c>
       <c r="L69" t="n">
         <v>-0.0008510638297871687</v>
@@ -3372,10 +3372,10 @@
         <v>-0.1703577512776795</v>
       </c>
       <c r="J70" t="n">
+        <v>69907</v>
+      </c>
+      <c r="K70" t="n">
         <v>819662</v>
-      </c>
-      <c r="K70" t="n">
-        <v>959414371</v>
       </c>
       <c r="L70" t="n">
         <v>-0.001703577512776833</v>
@@ -3414,10 +3414,10 @@
         <v>-0.170648464163834</v>
       </c>
       <c r="J71" t="n">
+        <v>78977</v>
+      </c>
+      <c r="K71" t="n">
         <v>924431</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1082970916.5</v>
       </c>
       <c r="L71" t="n">
         <v>-0.001706484641638362</v>
@@ -3456,10 +3456,10 @@
         <v>0.4273504273504335</v>
       </c>
       <c r="J72" t="n">
+        <v>73362</v>
+      </c>
+      <c r="K72" t="n">
         <v>860539</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1009412247</v>
       </c>
       <c r="L72" t="n">
         <v>0.004273504273504258</v>
@@ -3498,10 +3498,10 @@
         <v>0.1702127659574432</v>
       </c>
       <c r="J73" t="n">
+        <v>67432</v>
+      </c>
+      <c r="K73" t="n">
         <v>792668</v>
-      </c>
-      <c r="K73" t="n">
-        <v>931583067</v>
       </c>
       <c r="L73" t="n">
         <v>0.001702127659574337</v>
@@ -3540,10 +3540,10 @@
         <v>0.6796941376380635</v>
       </c>
       <c r="J74" t="n">
+        <v>81620</v>
+      </c>
+      <c r="K74" t="n">
         <v>963932</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1136957794</v>
       </c>
       <c r="L74" t="n">
         <v>0.00679694137638065</v>
@@ -3582,10 +3582,10 @@
         <v>-1.097046413502101</v>
       </c>
       <c r="J75" t="n">
+        <v>79863</v>
+      </c>
+      <c r="K75" t="n">
         <v>940385</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1108008626.25</v>
       </c>
       <c r="L75" t="n">
         <v>-0.01097046413502101</v>
@@ -3624,10 +3624,10 @@
         <v>-0.5972696245733812</v>
       </c>
       <c r="J76" t="n">
+        <v>71982</v>
+      </c>
+      <c r="K76" t="n">
         <v>840387</v>
-      </c>
-      <c r="K76" t="n">
-        <v>981151822.5</v>
       </c>
       <c r="L76" t="n">
         <v>-0.005972696245733822</v>
@@ -3666,10 +3666,10 @@
         <v>-0.0858369098712428</v>
       </c>
       <c r="J77" t="n">
+        <v>60777</v>
+      </c>
+      <c r="K77" t="n">
         <v>708048</v>
-      </c>
-      <c r="K77" t="n">
-        <v>825229944</v>
       </c>
       <c r="L77" t="n">
         <v>-0.0008583690987123971</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
+        <v>66248</v>
+      </c>
+      <c r="K78" t="n">
         <v>771129</v>
-      </c>
-      <c r="K78" t="n">
-        <v>897015809.25</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>-1.975945017182134</v>
       </c>
       <c r="J79" t="n">
+        <v>120222</v>
+      </c>
+      <c r="K79" t="n">
         <v>1386160</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1597549400</v>
       </c>
       <c r="L79" t="n">
         <v>-0.01975945017182135</v>
@@ -3792,10 +3792,10 @@
         <v>0.3505696757230425</v>
       </c>
       <c r="J80" t="n">
+        <v>73023</v>
+      </c>
+      <c r="K80" t="n">
         <v>834651</v>
-      </c>
-      <c r="K80" t="n">
-        <v>954423418.5</v>
       </c>
       <c r="L80" t="n">
         <v>0.003505696757230448</v>
@@ -3834,10 +3834,10 @@
         <v>-0.61135371179038</v>
       </c>
       <c r="J81" t="n">
+        <v>52270</v>
+      </c>
+      <c r="K81" t="n">
         <v>596402</v>
-      </c>
-      <c r="K81" t="n">
-        <v>680792883</v>
       </c>
       <c r="L81" t="n">
         <v>-0.006113537117903856</v>
@@ -3876,10 +3876,10 @@
         <v>1.230228471001747</v>
       </c>
       <c r="J82" t="n">
+        <v>117207</v>
+      </c>
+      <c r="K82" t="n">
         <v>1341430</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1535601992.5</v>
       </c>
       <c r="L82" t="n">
         <v>0.01230228471001737</v>
@@ -3918,10 +3918,10 @@
         <v>-0.5208333333333223</v>
       </c>
       <c r="J83" t="n">
+        <v>99224</v>
+      </c>
+      <c r="K83" t="n">
         <v>1139583</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1311090241.5</v>
       </c>
       <c r="L83" t="n">
         <v>-0.005208333333333259</v>
@@ -3960,10 +3960,10 @@
         <v>-0.5235602094240881</v>
       </c>
       <c r="J84" t="n">
+        <v>67742</v>
+      </c>
+      <c r="K84" t="n">
         <v>773276</v>
-      </c>
-      <c r="K84" t="n">
-        <v>882694554</v>
       </c>
       <c r="L84" t="n">
         <v>-0.005235602094240899</v>
@@ -4002,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
+        <v>66103</v>
+      </c>
+      <c r="K85" t="n">
         <v>753239</v>
-      </c>
-      <c r="K85" t="n">
-        <v>857750911.25</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4044,10 +4044,10 @@
         <v>-0.2631578947368521</v>
       </c>
       <c r="J86" t="n">
+        <v>103295</v>
+      </c>
+      <c r="K86" t="n">
         <v>1176012</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1338301656</v>
       </c>
       <c r="L86" t="n">
         <v>-0.00263157894736854</v>
@@ -4086,10 +4086,10 @@
         <v>-0.2638522427440577</v>
       </c>
       <c r="J87" t="n">
+        <v>73314</v>
+      </c>
+      <c r="K87" t="n">
         <v>832479</v>
-      </c>
-      <c r="K87" t="n">
-        <v>944239305.75</v>
       </c>
       <c r="L87" t="n">
         <v>-0.002638522427440559</v>
@@ -4128,10 +4128,10 @@
         <v>0.5291005291005335</v>
       </c>
       <c r="J88" t="n">
+        <v>92166</v>
+      </c>
+      <c r="K88" t="n">
         <v>1047469</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1189139182.25</v>
       </c>
       <c r="L88" t="n">
         <v>0.005291005291005346</v>
@@ -4170,10 +4170,10 @@
         <v>0.2631578947368365</v>
       </c>
       <c r="J89" t="n">
+        <v>95434</v>
+      </c>
+      <c r="K89" t="n">
         <v>1087948</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1241620655</v>
       </c>
       <c r="L89" t="n">
         <v>0.002631578947368318</v>
@@ -4212,10 +4212,10 @@
         <v>-0.2624671916010443</v>
       </c>
       <c r="J90" t="n">
+        <v>102888</v>
+      </c>
+      <c r="K90" t="n">
         <v>1168802</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1328343473</v>
       </c>
       <c r="L90" t="n">
         <v>-0.002624671916010457</v>
@@ -4254,10 +4254,10 @@
         <v>1.491228070175438</v>
       </c>
       <c r="J91" t="n">
+        <v>160577</v>
+      </c>
+      <c r="K91" t="n">
         <v>1843428</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2116255344</v>
       </c>
       <c r="L91" t="n">
         <v>0.01491228070175432</v>
@@ -4296,10 +4296,10 @@
         <v>-1.469317199654278</v>
       </c>
       <c r="J92" t="n">
+        <v>111791</v>
+      </c>
+      <c r="K92" t="n">
         <v>1271061</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1443289765.5</v>
       </c>
       <c r="L92" t="n">
         <v>-0.01469317199654274</v>
@@ -4338,10 +4338,10 @@
         <v>1.228070175438586</v>
       </c>
       <c r="J93" t="n">
+        <v>110117</v>
+      </c>
+      <c r="K93" t="n">
         <v>1261937</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1445864317.75</v>
       </c>
       <c r="L93" t="n">
         <v>0.01228070175438578</v>
@@ -4380,10 +4380,10 @@
         <v>-1.21317157712304</v>
       </c>
       <c r="J94" t="n">
+        <v>90801</v>
+      </c>
+      <c r="K94" t="n">
         <v>1039666</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1191977069</v>
       </c>
       <c r="L94" t="n">
         <v>-0.0121317157712304</v>
@@ -4422,10 +4422,10 @@
         <v>0.1754385964912243</v>
       </c>
       <c r="J95" t="n">
+        <v>83455</v>
+      </c>
+      <c r="K95" t="n">
         <v>952641</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1084819938.75</v>
       </c>
       <c r="L95" t="n">
         <v>0.001754385964912286</v>
@@ -4464,10 +4464,10 @@
         <v>0.08756567425568991</v>
       </c>
       <c r="J96" t="n">
+        <v>66681</v>
+      </c>
+      <c r="K96" t="n">
         <v>761165</v>
-      </c>
-      <c r="K96" t="n">
-        <v>869440721.25</v>
       </c>
       <c r="L96" t="n">
         <v>0.0008756567425569628</v>
@@ -4506,10 +4506,10 @@
         <v>0.7874015748031484</v>
       </c>
       <c r="J97" t="n">
+        <v>72749</v>
+      </c>
+      <c r="K97" t="n">
         <v>833703</v>
-      </c>
-      <c r="K97" t="n">
-        <v>955840489.5</v>
       </c>
       <c r="L97" t="n">
         <v>0.007874015748031482</v>
@@ -4548,10 +4548,10 @@
         <v>0.9548611111111216</v>
       </c>
       <c r="J98" t="n">
+        <v>118627</v>
+      </c>
+      <c r="K98" t="n">
         <v>1373112</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1591436808</v>
       </c>
       <c r="L98" t="n">
         <v>0.00954861111111116</v>
@@ -4590,10 +4590,10 @@
         <v>-0.6018916595012922</v>
       </c>
       <c r="J99" t="n">
+        <v>84670</v>
+      </c>
+      <c r="K99" t="n">
         <v>980475</v>
-      </c>
-      <c r="K99" t="n">
-        <v>1137105881.25</v>
       </c>
       <c r="L99" t="n">
         <v>-0.006018916595012969</v>
@@ -4632,10 +4632,10 @@
         <v>-0.3460207612456827</v>
       </c>
       <c r="J100" t="n">
+        <v>107501</v>
+      </c>
+      <c r="K100" t="n">
         <v>1239485</v>
-      </c>
-      <c r="K100" t="n">
-        <v>1428816333.75</v>
       </c>
       <c r="L100" t="n">
         <v>-0.0034602076124568</v>
@@ -4674,10 +4674,10 @@
         <v>-0.4340277777777685</v>
       </c>
       <c r="J101" t="n">
+        <v>71441</v>
+      </c>
+      <c r="K101" t="n">
         <v>821568</v>
-      </c>
-      <c r="K101" t="n">
-        <v>944803200</v>
       </c>
       <c r="L101" t="n">
         <v>-0.004340277777777679</v>
@@ -4716,10 +4716,10 @@
         <v>-0.6974716652136013</v>
       </c>
       <c r="J102" t="n">
+        <v>84570</v>
+      </c>
+      <c r="K102" t="n">
         <v>966214</v>
-      </c>
-      <c r="K102" t="n">
-        <v>1103174834.5</v>
       </c>
       <c r="L102" t="n">
         <v>-0.006974716652136004</v>
@@ -4758,10 +4758,10 @@
         <v>-0.08779631255487082</v>
       </c>
       <c r="J103" t="n">
+        <v>82932</v>
+      </c>
+      <c r="K103" t="n">
         <v>943770</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1075661857.5</v>
       </c>
       <c r="L103" t="n">
         <v>-0.0008779631255486642</v>
@@ -4800,10 +4800,10 @@
         <v>-0.5272407732864718</v>
       </c>
       <c r="J104" t="n">
+        <v>85480</v>
+      </c>
+      <c r="K104" t="n">
         <v>970193</v>
-      </c>
-      <c r="K104" t="n">
-        <v>1101169055</v>
       </c>
       <c r="L104" t="n">
         <v>-0.005272407732864748</v>
@@ -4842,10 +4842,10 @@
         <v>0.9717314487632458</v>
       </c>
       <c r="J105" t="n">
+        <v>83647</v>
+      </c>
+      <c r="K105" t="n">
         <v>952326</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1083508906.5</v>
       </c>
       <c r="L105" t="n">
         <v>0.009717314487632356</v>
@@ -4884,10 +4884,10 @@
         <v>1.399825021872267</v>
       </c>
       <c r="J106" t="n">
+        <v>130639</v>
+      </c>
+      <c r="K106" t="n">
         <v>1503007</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1730336808.75</v>
       </c>
       <c r="L106" t="n">
         <v>0.01399825021872259</v>
@@ -4926,10 +4926,10 @@
         <v>-0.6039689387402958</v>
       </c>
       <c r="J107" t="n">
+        <v>68795</v>
+      </c>
+      <c r="K107" t="n">
         <v>794926</v>
-      </c>
-      <c r="K107" t="n">
-        <v>918338261.5</v>
       </c>
       <c r="L107" t="n">
         <v>-0.006039689387402958</v>
@@ -4968,10 +4968,10 @@
         <v>-0.08680555555555371</v>
       </c>
       <c r="J108" t="n">
+        <v>66631</v>
+      </c>
+      <c r="K108" t="n">
         <v>766585</v>
-      </c>
-      <c r="K108" t="n">
-        <v>882722627.5</v>
       </c>
       <c r="L108" t="n">
         <v>-0.0008680555555555802</v>
@@ -5010,10 +5010,10 @@
         <v>0.3475238922676014</v>
       </c>
       <c r="J109" t="n">
+        <v>63706</v>
+      </c>
+      <c r="K109" t="n">
         <v>734851</v>
-      </c>
-      <c r="K109" t="n">
-        <v>847834341.25</v>
       </c>
       <c r="L109" t="n">
         <v>0.003475238922675983</v>
@@ -5052,10 +5052,10 @@
         <v>0.6926406926406933</v>
       </c>
       <c r="J110" t="n">
+        <v>71465</v>
+      </c>
+      <c r="K110" t="n">
         <v>827208</v>
-      </c>
-      <c r="K110" t="n">
-        <v>956252448</v>
       </c>
       <c r="L110" t="n">
         <v>0.006926406926407003</v>
@@ -5094,10 +5094,10 @@
         <v>0.3439380911435868</v>
       </c>
       <c r="J111" t="n">
+        <v>76128</v>
+      </c>
+      <c r="K111" t="n">
         <v>886509</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1031674848.75</v>
       </c>
       <c r="L111" t="n">
         <v>0.003439380911435919</v>
@@ -5136,10 +5136,10 @@
         <v>0.08568980291345148</v>
       </c>
       <c r="J112" t="n">
+        <v>97633</v>
+      </c>
+      <c r="K112" t="n">
         <v>1141325</v>
-      </c>
-      <c r="K112" t="n">
-        <v>1335920912.5</v>
       </c>
       <c r="L112" t="n">
         <v>0.0008568980291345785</v>
@@ -5178,10 +5178,10 @@
         <v>0.1712328767123251</v>
       </c>
       <c r="J113" t="n">
+        <v>83746</v>
+      </c>
+      <c r="K113" t="n">
         <v>978991</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1142237749.25</v>
       </c>
       <c r="L113" t="n">
         <v>0.001712328767123239</v>
@@ -5220,10 +5220,10 @@
         <v>0.4273504273504335</v>
       </c>
       <c r="J114" t="n">
+        <v>112468</v>
+      </c>
+      <c r="K114" t="n">
         <v>1316995</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1544835135</v>
       </c>
       <c r="L114" t="n">
         <v>0.004273504273504258</v>
@@ -5262,10 +5262,10 @@
         <v>-0.6808510638297879</v>
       </c>
       <c r="J115" t="n">
+        <v>84990</v>
+      </c>
+      <c r="K115" t="n">
         <v>995233</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1164173801.75</v>
       </c>
       <c r="L115" t="n">
         <v>-0.006808510638297904</v>
@@ -5304,10 +5304,10 @@
         <v>-0.685518423307627</v>
       </c>
       <c r="J116" t="n">
+        <v>57666</v>
+      </c>
+      <c r="K116" t="n">
         <v>670077</v>
-      </c>
-      <c r="K116" t="n">
-        <v>778964512.5</v>
       </c>
       <c r="L116" t="n">
         <v>-0.006855184233076295</v>
@@ -5346,10 +5346,10 @@
         <v>1.811906816220887</v>
       </c>
       <c r="J117" t="n">
+        <v>114200</v>
+      </c>
+      <c r="K117" t="n">
         <v>1334996</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1561277822</v>
       </c>
       <c r="L117" t="n">
         <v>0.01811906816220898</v>
@@ -5388,10 +5388,10 @@
         <v>0.423728813559313</v>
       </c>
       <c r="J118" t="n">
+        <v>138497</v>
+      </c>
+      <c r="K118" t="n">
         <v>1637040</v>
-      </c>
-      <c r="K118" t="n">
-        <v>1938664620</v>
       </c>
       <c r="L118" t="n">
         <v>0.004237288135593209</v>
@@ -5430,10 +5430,10 @@
         <v>-1.350210970464136</v>
       </c>
       <c r="J119" t="n">
+        <v>124764</v>
+      </c>
+      <c r="K119" t="n">
         <v>1465359</v>
-      </c>
-      <c r="K119" t="n">
-        <v>1722895844.25</v>
       </c>
       <c r="L119" t="n">
         <v>-0.01350210970464139</v>
@@ -5472,10 +5472,10 @@
         <v>-0.7698887938408885</v>
       </c>
       <c r="J120" t="n">
+        <v>95890</v>
+      </c>
+      <c r="K120" t="n">
         <v>1117119</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1302281474.25</v>
       </c>
       <c r="L120" t="n">
         <v>-0.007698887938408894</v>
@@ -5514,10 +5514,10 @@
         <v>1.724137931034492</v>
       </c>
       <c r="J121" t="n">
+        <v>87833</v>
+      </c>
+      <c r="K121" t="n">
         <v>1028081</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1202597749.75</v>
       </c>
       <c r="L121" t="n">
         <v>0.01724137931034497</v>
@@ -5556,10 +5556,10 @@
         <v>-0.9322033898305185</v>
       </c>
       <c r="J122" t="n">
+        <v>69898</v>
+      </c>
+      <c r="K122" t="n">
         <v>821301</v>
-      </c>
-      <c r="K122" t="n">
-        <v>965028675</v>
       </c>
       <c r="L122" t="n">
         <v>-0.009322033898305215</v>
@@ -5598,10 +5598,10 @@
         <v>0.1710863986313204</v>
       </c>
       <c r="J123" t="n">
+        <v>86594</v>
+      </c>
+      <c r="K123" t="n">
         <v>1011847</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1180319525.5</v>
       </c>
       <c r="L123" t="n">
         <v>0.00171086398631326</v>
@@ -5640,10 +5640,10 @@
         <v>-0.8539709649872026</v>
       </c>
       <c r="J124" t="n">
+        <v>75976</v>
+      </c>
+      <c r="K124" t="n">
         <v>884358</v>
-      </c>
-      <c r="K124" t="n">
-        <v>1028950533</v>
       </c>
       <c r="L124" t="n">
         <v>-0.008539709649872052</v>
@@ -5682,10 +5682,10 @@
         <v>0.6890611541774339</v>
       </c>
       <c r="J125" t="n">
+        <v>89079</v>
+      </c>
+      <c r="K125" t="n">
         <v>1037323</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1206406649</v>
       </c>
       <c r="L125" t="n">
         <v>0.006890611541774394</v>
@@ -5724,10 +5724,10 @@
         <v>-0.4277159965782629</v>
       </c>
       <c r="J126" t="n">
+        <v>65871</v>
+      </c>
+      <c r="K126" t="n">
         <v>768060</v>
-      </c>
-      <c r="K126" t="n">
-        <v>895557960</v>
       </c>
       <c r="L126" t="n">
         <v>-0.004277159965782595</v>
@@ -5766,10 +5766,10 @@
         <v>-0.7731958762886585</v>
       </c>
       <c r="J127" t="n">
+        <v>81466</v>
+      </c>
+      <c r="K127" t="n">
         <v>944601</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1096445610.75</v>
       </c>
       <c r="L127" t="n">
         <v>-0.00773195876288657</v>
@@ -5808,10 +5808,10 @@
         <v>-0.5194805194805238</v>
       </c>
       <c r="J128" t="n">
+        <v>76918</v>
+      </c>
+      <c r="K128" t="n">
         <v>886090</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1020775680</v>
       </c>
       <c r="L128" t="n">
         <v>-0.005194805194805197</v>
@@ -5850,10 +5850,10 @@
         <v>0.3481288076588264</v>
       </c>
       <c r="J129" t="n">
+        <v>77391</v>
+      </c>
+      <c r="K129" t="n">
         <v>890766</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1023490134</v>
       </c>
       <c r="L129" t="n">
         <v>0.003481288076588207</v>
@@ -5892,10 +5892,10 @@
         <v>-0.08673026886383163</v>
       </c>
       <c r="J130" t="n">
+        <v>74394</v>
+      </c>
+      <c r="K130" t="n">
         <v>855899</v>
-      </c>
-      <c r="K130" t="n">
-        <v>986209622.75</v>
       </c>
       <c r="L130" t="n">
         <v>-0.0008673026886383273</v>
@@ -5934,10 +5934,10 @@
         <v>-0.7812499999999988</v>
       </c>
       <c r="J131" t="n">
+        <v>63961</v>
+      </c>
+      <c r="K131" t="n">
         <v>733957</v>
-      </c>
-      <c r="K131" t="n">
-        <v>842582636</v>
       </c>
       <c r="L131" t="n">
         <v>-0.0078125</v>
@@ -5976,10 +5976,10 @@
         <v>-0.8748906386701631</v>
       </c>
       <c r="J132" t="n">
+        <v>91705</v>
+      </c>
+      <c r="K132" t="n">
         <v>1044065</v>
-      </c>
-      <c r="K132" t="n">
-        <v>1188145970</v>
       </c>
       <c r="L132" t="n">
         <v>-0.008748906386701671</v>
@@ -6018,10 +6018,10 @@
         <v>0.3530450132391805</v>
       </c>
       <c r="J133" t="n">
+        <v>81449</v>
+      </c>
+      <c r="K133" t="n">
         <v>925261</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1050402550.25</v>
       </c>
       <c r="L133" t="n">
         <v>0.003530450132391838</v>
@@ -6060,10 +6060,10 @@
         <v>-0.1759014951627051</v>
       </c>
       <c r="J134" t="n">
+        <v>104920</v>
+      </c>
+      <c r="K134" t="n">
         <v>1191895</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1354290693.75</v>
       </c>
       <c r="L134" t="n">
         <v>-0.001759014951627003</v>
@@ -6102,10 +6102,10 @@
         <v>1.409691629955948</v>
       </c>
       <c r="J135" t="n">
+        <v>82349</v>
+      </c>
+      <c r="K135" t="n">
         <v>940833</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1075372119</v>
       </c>
       <c r="L135" t="n">
         <v>0.01409691629955945</v>
@@ -6144,10 +6144,10 @@
         <v>-0.2606429192006895</v>
       </c>
       <c r="J136" t="n">
+        <v>56365</v>
+      </c>
+      <c r="K136" t="n">
         <v>647351</v>
-      </c>
-      <c r="K136" t="n">
-        <v>743806299</v>
       </c>
       <c r="L136" t="n">
         <v>-0.002606429192006932</v>
@@ -6186,10 +6186,10 @@
         <v>0.4355400696864019</v>
       </c>
       <c r="J137" t="n">
+        <v>61000</v>
+      </c>
+      <c r="K137" t="n">
         <v>701495</v>
-      </c>
-      <c r="K137" t="n">
-        <v>806719250</v>
       </c>
       <c r="L137" t="n">
         <v>0.00435540069686402</v>
@@ -6228,10 +6228,10 @@
         <v>0.9540329575021788</v>
       </c>
       <c r="J138" t="n">
+        <v>68291</v>
+      </c>
+      <c r="K138" t="n">
         <v>790467</v>
-      </c>
-      <c r="K138" t="n">
-        <v>914570319</v>
       </c>
       <c r="L138" t="n">
         <v>0.009540329575021822</v>
@@ -6270,10 +6270,10 @@
         <v>-0.171821305841936</v>
       </c>
       <c r="J139" t="n">
+        <v>55904</v>
+      </c>
+      <c r="K139" t="n">
         <v>649886</v>
-      </c>
-      <c r="K139" t="n">
-        <v>755167532</v>
       </c>
       <c r="L139" t="n">
         <v>-0.001718213058419349</v>
@@ -6312,10 +6312,10 @@
         <v>-0.8605851979345925</v>
       </c>
       <c r="J140" t="n">
+        <v>64191</v>
+      </c>
+      <c r="K140" t="n">
         <v>742369</v>
-      </c>
-      <c r="K140" t="n">
-        <v>858364156.25</v>
       </c>
       <c r="L140" t="n">
         <v>-0.008605851979345935</v>
@@ -6354,10 +6354,10 @@
         <v>0.3472222222222303</v>
       </c>
       <c r="J141" t="n">
+        <v>57735</v>
+      </c>
+      <c r="K141" t="n">
         <v>666266</v>
-      </c>
-      <c r="K141" t="n">
-        <v>769204097</v>
       </c>
       <c r="L141" t="n">
         <v>0.003472222222222321</v>
@@ -6396,10 +6396,10 @@
         <v>-0.173010380622849</v>
       </c>
       <c r="J142" t="n">
+        <v>43763</v>
+      </c>
+      <c r="K142" t="n">
         <v>505244</v>
-      </c>
-      <c r="K142" t="n">
-        <v>583051576</v>
       </c>
       <c r="L142" t="n">
         <v>-0.001730103806228511</v>
@@ -6438,10 +6438,10 @@
         <v>0.1733102253033046</v>
       </c>
       <c r="J143" t="n">
+        <v>47399</v>
+      </c>
+      <c r="K143" t="n">
         <v>547455</v>
-      </c>
-      <c r="K143" t="n">
-        <v>632857980</v>
       </c>
       <c r="L143" t="n">
         <v>0.001733102253033136</v>
@@ -6480,10 +6480,10 @@
         <v>-0.173010380622849</v>
       </c>
       <c r="J144" t="n">
+        <v>37778</v>
+      </c>
+      <c r="K144" t="n">
         <v>436340</v>
-      </c>
-      <c r="K144" t="n">
-        <v>504190870</v>
       </c>
       <c r="L144" t="n">
         <v>-0.001730103806228511</v>
@@ -6522,10 +6522,10 @@
         <v>0.1733102253033046</v>
       </c>
       <c r="J145" t="n">
+        <v>56129</v>
+      </c>
+      <c r="K145" t="n">
         <v>648295</v>
-      </c>
-      <c r="K145" t="n">
-        <v>749104872.5</v>
       </c>
       <c r="L145" t="n">
         <v>0.001733102253033136</v>
@@ -6564,10 +6564,10 @@
         <v>-0.6920415224913501</v>
       </c>
       <c r="J146" t="n">
+        <v>50637</v>
+      </c>
+      <c r="K146" t="n">
         <v>582584</v>
-      </c>
-      <c r="K146" t="n">
-        <v>670262892</v>
       </c>
       <c r="L146" t="n">
         <v>-0.00692041522491349</v>
@@ -6606,10 +6606,10 @@
         <v>-0.609756097560978</v>
       </c>
       <c r="J147" t="n">
+        <v>51605</v>
+      </c>
+      <c r="K147" t="n">
         <v>590620</v>
-      </c>
-      <c r="K147" t="n">
-        <v>675964590</v>
       </c>
       <c r="L147" t="n">
         <v>-0.006097560975609762</v>
@@ -6648,10 +6648,10 @@
         <v>0.7887817703768611</v>
       </c>
       <c r="J148" t="n">
+        <v>76395</v>
+      </c>
+      <c r="K148" t="n">
         <v>875491</v>
-      </c>
-      <c r="K148" t="n">
-        <v>1003312686</v>
       </c>
       <c r="L148" t="n">
         <v>0.007887817703768674</v>
@@ -6690,10 +6690,10 @@
         <v>1.478260869565217</v>
       </c>
       <c r="J149" t="n">
+        <v>112615</v>
+      </c>
+      <c r="K149" t="n">
         <v>1304648</v>
-      </c>
-      <c r="K149" t="n">
-        <v>1511108546</v>
       </c>
       <c r="L149" t="n">
         <v>0.01478260869565218</v>
@@ -6732,10 +6732,10 @@
         <v>-0.2570694087403544</v>
       </c>
       <c r="J150" t="n">
+        <v>82939</v>
+      </c>
+      <c r="K150" t="n">
         <v>966236</v>
-      </c>
-      <c r="K150" t="n">
-        <v>1129046766</v>
       </c>
       <c r="L150" t="n">
         <v>-0.002570694087403513</v>
@@ -6774,10 +6774,10 @@
         <v>-1.116838487972515</v>
       </c>
       <c r="J151" t="n">
+        <v>95040</v>
+      </c>
+      <c r="K151" t="n">
         <v>1100085</v>
-      </c>
-      <c r="K151" t="n">
-        <v>1273073366.25</v>
       </c>
       <c r="L151" t="n">
         <v>-0.01116838487972516</v>
@@ -6816,10 +6816,10 @@
         <v>-0.4344048653344825</v>
       </c>
       <c r="J152" t="n">
+        <v>85549</v>
+      </c>
+      <c r="K152" t="n">
         <v>983390</v>
-      </c>
-      <c r="K152" t="n">
-        <v>1129915110</v>
       </c>
       <c r="L152" t="n">
         <v>-0.004344048653344812</v>
@@ -6858,10 +6858,10 @@
         <v>0.1745200698080242</v>
       </c>
       <c r="J153" t="n">
+        <v>74593</v>
+      </c>
+      <c r="K153" t="n">
         <v>855213</v>
-      </c>
-      <c r="K153" t="n">
-        <v>980074098</v>
       </c>
       <c r="L153" t="n">
         <v>0.001745200698080263</v>
@@ -6900,10 +6900,10 @@
         <v>-0.08710801393728036</v>
       </c>
       <c r="J154" t="n">
+        <v>92509</v>
+      </c>
+      <c r="K154" t="n">
         <v>1061541</v>
-      </c>
-      <c r="K154" t="n">
-        <v>1218914453.25</v>
       </c>
       <c r="L154" t="n">
         <v>-0.0008710801393727596</v>
@@ -6942,10 +6942,10 @@
         <v>-0.9590235396687115</v>
       </c>
       <c r="J155" t="n">
+        <v>111674</v>
+      </c>
+      <c r="K155" t="n">
         <v>1274757</v>
-      </c>
-      <c r="K155" t="n">
-        <v>1454816426.25</v>
       </c>
       <c r="L155" t="n">
         <v>-0.00959023539668713</v>
@@ -6984,10 +6984,10 @@
         <v>-0.4401408450704132</v>
       </c>
       <c r="J156" t="n">
+        <v>78177</v>
+      </c>
+      <c r="K156" t="n">
         <v>884960</v>
-      </c>
-      <c r="K156" t="n">
-        <v>1002438440</v>
       </c>
       <c r="L156" t="n">
         <v>-0.004401408450704136</v>
@@ -7026,10 +7026,10 @@
         <v>-1.06100795755969</v>
       </c>
       <c r="J157" t="n">
+        <v>99376</v>
+      </c>
+      <c r="K157" t="n">
         <v>1119473</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1260246729.75</v>
       </c>
       <c r="L157" t="n">
         <v>-0.0106100795755969</v>
@@ -7068,10 +7068,10 @@
         <v>-0.625558534405722</v>
       </c>
       <c r="J158" t="n">
+        <v>72271</v>
+      </c>
+      <c r="K158" t="n">
         <v>804741</v>
-      </c>
-      <c r="K158" t="n">
-        <v>897085029.75</v>
       </c>
       <c r="L158" t="n">
         <v>-0.006255585344057235</v>
@@ -7110,10 +7110,10 @@
         <v>0.3597122302158357</v>
       </c>
       <c r="J159" t="n">
+        <v>69325</v>
+      </c>
+      <c r="K159" t="n">
         <v>772276</v>
-      </c>
-      <c r="K159" t="n">
-        <v>860894671</v>
       </c>
       <c r="L159" t="n">
         <v>0.003597122302158251</v>
@@ -7152,10 +7152,10 @@
         <v>-0.8064516129032245</v>
       </c>
       <c r="J160" t="n">
+        <v>81019</v>
+      </c>
+      <c r="K160" t="n">
         <v>900125</v>
-      </c>
-      <c r="K160" t="n">
-        <v>1000488937.5</v>
       </c>
       <c r="L160" t="n">
         <v>-0.008064516129032251</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
+        <v>71241</v>
+      </c>
+      <c r="K161" t="n">
         <v>788635</v>
-      </c>
-      <c r="K161" t="n">
-        <v>874201897.5</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7236,10 +7236,10 @@
         <v>-0.7226738934056014</v>
       </c>
       <c r="J162" t="n">
+        <v>100634</v>
+      </c>
+      <c r="K162" t="n">
         <v>1109994</v>
-      </c>
-      <c r="K162" t="n">
-        <v>1224600880.5</v>
       </c>
       <c r="L162" t="n">
         <v>-0.00722673893405601</v>
@@ -7278,10 +7278,10 @@
         <v>-0.2729754322110952</v>
       </c>
       <c r="J163" t="n">
+        <v>100843</v>
+      </c>
+      <c r="K163" t="n">
         <v>1106247</v>
-      </c>
-      <c r="K163" t="n">
-        <v>1214659206</v>
       </c>
       <c r="L163" t="n">
         <v>-0.002729754322110978</v>
@@ -7320,10 +7320,10 @@
         <v>-0.1824817518248298</v>
       </c>
       <c r="J164" t="n">
+        <v>81652</v>
+      </c>
+      <c r="K164" t="n">
         <v>894091</v>
-      </c>
-      <c r="K164" t="n">
-        <v>980370781.5</v>
       </c>
       <c r="L164" t="n">
         <v>-0.001824817518248256</v>
@@ -7362,10 +7362,10 @@
         <v>-0.9140767824497225</v>
       </c>
       <c r="J165" t="n">
+        <v>132118</v>
+      </c>
+      <c r="K165" t="n">
         <v>1438766</v>
-      </c>
-      <c r="K165" t="n">
-        <v>1567895248.5</v>
       </c>
       <c r="L165" t="n">
         <v>-0.009140767824497242</v>
@@ -7404,10 +7404,10 @@
         <v>1.10701107011071</v>
       </c>
       <c r="J166" t="n">
+        <v>169999</v>
+      </c>
+      <c r="K166" t="n">
         <v>1852994</v>
-      </c>
-      <c r="K166" t="n">
-        <v>2012351484</v>
       </c>
       <c r="L166" t="n">
         <v>0.01107011070110708</v>
@@ -7446,10 +7446,10 @@
         <v>-1.186131386861321</v>
       </c>
       <c r="J167" t="n">
+        <v>100299</v>
+      </c>
+      <c r="K167" t="n">
         <v>1091755</v>
-      </c>
-      <c r="K167" t="n">
-        <v>1190831766.25</v>
       </c>
       <c r="L167" t="n">
         <v>-0.01186131386861322</v>
@@ -7488,10 +7488,10 @@
         <v>0.2770083102493016</v>
       </c>
       <c r="J168" t="n">
+        <v>112839</v>
+      </c>
+      <c r="K168" t="n">
         <v>1223173</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1330506430.75</v>
       </c>
       <c r="L168" t="n">
         <v>0.002770083102493048</v>
@@ -7530,10 +7530,10 @@
         <v>-0.1841620626150974</v>
       </c>
       <c r="J169" t="n">
+        <v>74241</v>
+      </c>
+      <c r="K169" t="n">
         <v>806628</v>
-      </c>
-      <c r="K169" t="n">
-        <v>875191380</v>
       </c>
       <c r="L169" t="n">
         <v>-0.001841620626151008</v>
@@ -7572,10 +7572,10 @@
         <v>1.199261992619933</v>
       </c>
       <c r="J170" t="n">
+        <v>63741</v>
+      </c>
+      <c r="K170" t="n">
         <v>695415</v>
-      </c>
-      <c r="K170" t="n">
-        <v>758697765</v>
       </c>
       <c r="L170" t="n">
         <v>0.01199261992619927</v>
@@ -7614,10 +7614,10 @@
         <v>1.093892433910658</v>
       </c>
       <c r="J171" t="n">
+        <v>106714</v>
+      </c>
+      <c r="K171" t="n">
         <v>1177591</v>
-      </c>
-      <c r="K171" t="n">
-        <v>1299471668.5</v>
       </c>
       <c r="L171" t="n">
         <v>0.01093892433910648</v>
@@ -7656,10 +7656,10 @@
         <v>-0.3606853020739328</v>
       </c>
       <c r="J172" t="n">
+        <v>65767</v>
+      </c>
+      <c r="K172" t="n">
         <v>727710</v>
-      </c>
-      <c r="K172" t="n">
-        <v>805211115</v>
       </c>
       <c r="L172" t="n">
         <v>-0.003606853020739376</v>
@@ -7698,10 +7698,10 @@
         <v>0.1809954751131183</v>
       </c>
       <c r="J173" t="n">
+        <v>56032</v>
+      </c>
+      <c r="K173" t="n">
         <v>619717</v>
-      </c>
-      <c r="K173" t="n">
-        <v>685407002</v>
       </c>
       <c r="L173" t="n">
         <v>0.001809954751131215</v>
@@ -7740,10 +7740,10 @@
         <v>-0.09033423667569816</v>
       </c>
       <c r="J174" t="n">
+        <v>54264</v>
+      </c>
+      <c r="K174" t="n">
         <v>600430</v>
-      </c>
-      <c r="K174" t="n">
-        <v>664225687.5</v>
       </c>
       <c r="L174" t="n">
         <v>-0.0009033423667569318</v>
@@ -7782,10 +7782,10 @@
         <v>0.0904159132007214</v>
       </c>
       <c r="J175" t="n">
+        <v>38955</v>
+      </c>
+      <c r="K175" t="n">
         <v>431041</v>
-      </c>
-      <c r="K175" t="n">
-        <v>476731346</v>
       </c>
       <c r="L175" t="n">
         <v>0.0009041591320071429</v>
@@ -7824,10 +7824,10 @@
         <v>-0.9936766034326958</v>
       </c>
       <c r="J176" t="n">
+        <v>61856</v>
+      </c>
+      <c r="K176" t="n">
         <v>681340</v>
-      </c>
-      <c r="K176" t="n">
-        <v>750155340</v>
       </c>
       <c r="L176" t="n">
         <v>-0.009936766034326916</v>
@@ -7866,10 +7866,10 @@
         <v>-0.4562043795620503</v>
       </c>
       <c r="J177" t="n">
+        <v>50759</v>
+      </c>
+      <c r="K177" t="n">
         <v>555047</v>
-      </c>
-      <c r="K177" t="n">
-        <v>607221418</v>
       </c>
       <c r="L177" t="n">
         <v>-0.00456204379562053</v>
@@ -7908,10 +7908,10 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
+        <v>55175</v>
+      </c>
+      <c r="K178" t="n">
         <v>602512</v>
-      </c>
-      <c r="K178" t="n">
-        <v>657792476</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -7950,10 +7950,10 @@
         <v>-0.4582951420715005</v>
       </c>
       <c r="J179" t="n">
+        <v>97670</v>
+      </c>
+      <c r="K179" t="n">
         <v>1063135</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1156159312.5</v>
       </c>
       <c r="L179" t="n">
         <v>-0.004582951420714965</v>
@@ -7992,10 +7992,10 @@
         <v>0.09208103130754869</v>
       </c>
       <c r="J180" t="n">
+        <v>65599</v>
+      </c>
+      <c r="K180" t="n">
         <v>712730</v>
-      </c>
-      <c r="K180" t="n">
-        <v>774024780</v>
       </c>
       <c r="L180" t="n">
         <v>0.0009208103130755596</v>
@@ -8034,10 +8034,10 @@
         <v>0.2759889604415928</v>
       </c>
       <c r="J181" t="n">
+        <v>56271</v>
+      </c>
+      <c r="K181" t="n">
         <v>612228</v>
-      </c>
-      <c r="K181" t="n">
-        <v>666104064</v>
       </c>
       <c r="L181" t="n">
         <v>0.002759889604415866</v>
@@ -8076,10 +8076,10 @@
         <v>-0.4587155963302817</v>
       </c>
       <c r="J182" t="n">
+        <v>77316</v>
+      </c>
+      <c r="K182" t="n">
         <v>838874</v>
-      </c>
-      <c r="K182" t="n">
-        <v>909339416</v>
       </c>
       <c r="L182" t="n">
         <v>-0.004587155963302836</v>
@@ -8118,10 +8118,10 @@
         <v>0.2764976958525451</v>
       </c>
       <c r="J183" t="n">
+        <v>94680</v>
+      </c>
+      <c r="K183" t="n">
         <v>1028695</v>
-      </c>
-      <c r="K183" t="n">
-        <v>1118191465</v>
       </c>
       <c r="L183" t="n">
         <v>0.0027649769585254</v>
@@ -8160,10 +8160,10 @@
         <v>-1.562499999999999</v>
       </c>
       <c r="J184" t="n">
+        <v>101134</v>
+      </c>
+      <c r="K184" t="n">
         <v>1089714</v>
-      </c>
-      <c r="K184" t="n">
-        <v>1173077121</v>
       </c>
       <c r="L184" t="n">
         <v>-0.015625</v>
@@ -8202,10 +8202,10 @@
         <v>0.9337068160597539</v>
       </c>
       <c r="J185" t="n">
+        <v>66200</v>
+      </c>
+      <c r="K185" t="n">
         <v>712641</v>
-      </c>
-      <c r="K185" t="n">
-        <v>767336196.75</v>
       </c>
       <c r="L185" t="n">
         <v>0.009337068160597539</v>
@@ -8244,10 +8244,10 @@
         <v>0.09250693802034955</v>
       </c>
       <c r="J186" t="n">
+        <v>44128</v>
+      </c>
+      <c r="K186" t="n">
         <v>476577</v>
-      </c>
-      <c r="K186" t="n">
-        <v>514822304.25</v>
       </c>
       <c r="L186" t="n">
         <v>0.0009250693802034249</v>
@@ -8286,10 +8286,10 @@
         <v>-0.5545286506469547</v>
       </c>
       <c r="J187" t="n">
+        <v>77577</v>
+      </c>
+      <c r="K187" t="n">
         <v>835892</v>
-      </c>
-      <c r="K187" t="n">
-        <v>900882603</v>
       </c>
       <c r="L187" t="n">
         <v>-0.005545286506469571</v>
@@ -8328,10 +8328,10 @@
         <v>0.4646840148698951</v>
       </c>
       <c r="J188" t="n">
+        <v>73226</v>
+      </c>
+      <c r="K188" t="n">
         <v>790112</v>
-      </c>
-      <c r="K188" t="n">
-        <v>851740736</v>
       </c>
       <c r="L188" t="n">
         <v>0.004646840148698983</v>
@@ -8370,10 +8370,10 @@
         <v>0.7400555041628128</v>
       </c>
       <c r="J189" t="n">
+        <v>66470</v>
+      </c>
+      <c r="K189" t="n">
         <v>720535</v>
-      </c>
-      <c r="K189" t="n">
-        <v>780879806.25</v>
       </c>
       <c r="L189" t="n">
         <v>0.007400555041628065</v>
@@ -8412,10 +8412,10 @@
         <v>0.4591368227731766</v>
       </c>
       <c r="J190" t="n">
+        <v>69226</v>
+      </c>
+      <c r="K190" t="n">
         <v>754906</v>
-      </c>
-      <c r="K190" t="n">
-        <v>823224993</v>
       </c>
       <c r="L190" t="n">
         <v>0.004591368227731873</v>
@@ -8454,10 +8454,10 @@
         <v>-0.09140767824497063</v>
       </c>
       <c r="J191" t="n">
+        <v>77030</v>
+      </c>
+      <c r="K191" t="n">
         <v>841939</v>
-      </c>
-      <c r="K191" t="n">
-        <v>920449811.75</v>
       </c>
       <c r="L191" t="n">
         <v>-0.000914076782449702</v>
@@ -8496,10 +8496,10 @@
         <v>-0.09149130832570711</v>
       </c>
       <c r="J192" t="n">
+        <v>65501</v>
+      </c>
+      <c r="K192" t="n">
         <v>715603</v>
-      </c>
-      <c r="K192" t="n">
-        <v>781796277.5</v>
       </c>
       <c r="L192" t="n">
         <v>-0.0009149130832570851</v>
@@ -8538,10 +8538,10 @@
         <v>1.007326007326002</v>
       </c>
       <c r="J193" t="n">
+        <v>98146</v>
+      </c>
+      <c r="K193" t="n">
         <v>1076657</v>
-      </c>
-      <c r="K193" t="n">
-        <v>1181900221.75</v>
       </c>
       <c r="L193" t="n">
         <v>0.01007326007326004</v>
@@ -8580,10 +8580,10 @@
         <v>-0.634632819582942</v>
       </c>
       <c r="J194" t="n">
+        <v>71916</v>
+      </c>
+      <c r="K194" t="n">
         <v>791079</v>
-      </c>
-      <c r="K194" t="n">
-        <v>869198051.25</v>
       </c>
       <c r="L194" t="n">
         <v>-0.006346328195829476</v>
@@ -8622,10 +8622,10 @@
         <v>-0.7299270072992706</v>
       </c>
       <c r="J195" t="n">
+        <v>57267</v>
+      </c>
+      <c r="K195" t="n">
         <v>624212</v>
-      </c>
-      <c r="K195" t="n">
-        <v>680859239</v>
       </c>
       <c r="L195" t="n">
         <v>-0.007299270072992692</v>
@@ -8664,10 +8664,10 @@
         <v>-1.011029411764717</v>
       </c>
       <c r="J196" t="n">
+        <v>77087</v>
+      </c>
+      <c r="K196" t="n">
         <v>834083</v>
-      </c>
-      <c r="K196" t="n">
-        <v>903728930.5</v>
       </c>
       <c r="L196" t="n">
         <v>-0.01011029411764719</v>
@@ -8706,10 +8706,10 @@
         <v>-2.971216341689882</v>
       </c>
       <c r="J197" t="n">
+        <v>149559</v>
+      </c>
+      <c r="K197" t="n">
         <v>1580088</v>
-      </c>
-      <c r="K197" t="n">
-        <v>1668572928</v>
       </c>
       <c r="L197" t="n">
         <v>-0.02971216341689886</v>
@@ -8748,10 +8748,10 @@
         <v>4.114832535885182</v>
       </c>
       <c r="J198" t="n">
+        <v>151612</v>
+      </c>
+      <c r="K198" t="n">
         <v>1622251</v>
-      </c>
-      <c r="K198" t="n">
-        <v>1736214132.75</v>
       </c>
       <c r="L198" t="n">
         <v>0.04114832535885182</v>
@@ -8790,10 +8790,10 @@
         <v>0.5514705882352824</v>
       </c>
       <c r="J199" t="n">
+        <v>68235</v>
+      </c>
+      <c r="K199" t="n">
         <v>744780</v>
-      </c>
-      <c r="K199" t="n">
-        <v>811251615</v>
       </c>
       <c r="L199" t="n">
         <v>0.005514705882352811</v>
@@ -8832,10 +8832,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
+        <v>75759</v>
+      </c>
+      <c r="K200" t="n">
         <v>827664</v>
-      </c>
-      <c r="K200" t="n">
-        <v>906292080</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -8874,10 +8874,10 @@
         <v>0.7312614259597813</v>
       </c>
       <c r="J201" t="n">
+        <v>80632</v>
+      </c>
+      <c r="K201" t="n">
         <v>884129</v>
-      </c>
-      <c r="K201" t="n">
-        <v>968342287.25</v>
       </c>
       <c r="L201" t="n">
         <v>0.007312614259597838</v>
@@ -8916,10 +8916,10 @@
         <v>-0.2722323049001757</v>
       </c>
       <c r="J202" t="n">
+        <v>57581</v>
+      </c>
+      <c r="K202" t="n">
         <v>632522</v>
-      </c>
-      <c r="K202" t="n">
-        <v>695141678</v>
       </c>
       <c r="L202" t="n">
         <v>-0.002722323049001774</v>
@@ -8958,10 +8958,10 @@
         <v>0.8189262966333016</v>
       </c>
       <c r="J203" t="n">
+        <v>105486</v>
+      </c>
+      <c r="K203" t="n">
         <v>1164565</v>
-      </c>
-      <c r="K203" t="n">
-        <v>1288300031.25</v>
       </c>
       <c r="L203" t="n">
         <v>0.008189262966332933</v>
@@ -9000,10 +9000,10 @@
         <v>0.6317689530685946</v>
       </c>
       <c r="J204" t="n">
+        <v>82637</v>
+      </c>
+      <c r="K204" t="n">
         <v>918925</v>
-      </c>
-      <c r="K204" t="n">
-        <v>1023452718.75</v>
       </c>
       <c r="L204" t="n">
         <v>0.00631768953068601</v>
@@ -9042,10 +9042,10 @@
         <v>1.076233183856495</v>
       </c>
       <c r="J205" t="n">
+        <v>102488</v>
+      </c>
+      <c r="K205" t="n">
         <v>1148895</v>
-      </c>
-      <c r="K205" t="n">
-        <v>1288772966.25</v>
       </c>
       <c r="L205" t="n">
         <v>0.01076233183856501</v>
@@ -9084,10 +9084,10 @@
         <v>-1.33096716947649</v>
       </c>
       <c r="J206" t="n">
+        <v>67657</v>
+      </c>
+      <c r="K206" t="n">
         <v>757757</v>
-      </c>
-      <c r="K206" t="n">
-        <v>848119522.25</v>
       </c>
       <c r="L206" t="n">
         <v>-0.01330967169476494</v>
@@ -9126,10 +9126,10 @@
         <v>-0.8093525179856103</v>
       </c>
       <c r="J207" t="n">
+        <v>54894</v>
+      </c>
+      <c r="K207" t="n">
         <v>607955</v>
-      </c>
-      <c r="K207" t="n">
-        <v>672702207.5</v>
       </c>
       <c r="L207" t="n">
         <v>-0.008093525179856065</v>
@@ -9168,10 +9168,10 @@
         <v>1.722574796010891</v>
       </c>
       <c r="J208" t="n">
+        <v>72815</v>
+      </c>
+      <c r="K208" t="n">
         <v>812976</v>
-      </c>
-      <c r="K208" t="n">
-        <v>906468240</v>
       </c>
       <c r="L208" t="n">
         <v>0.01722574796010901</v>
@@ -9210,10 +9210,10 @@
         <v>-1.069518716577549</v>
       </c>
       <c r="J209" t="n">
+        <v>54097</v>
+      </c>
+      <c r="K209" t="n">
         <v>602365</v>
-      </c>
-      <c r="K209" t="n">
-        <v>670884018.75</v>
       </c>
       <c r="L209" t="n">
         <v>-0.01069518716577544</v>
@@ -9252,10 +9252,10 @@
         <v>-0.09009009009008817</v>
       </c>
       <c r="J210" t="n">
+        <v>43357</v>
+      </c>
+      <c r="K210" t="n">
         <v>481047</v>
-      </c>
-      <c r="K210" t="n">
-        <v>533841908.25</v>
       </c>
       <c r="L210" t="n">
         <v>-0.0009009009009008917</v>
@@ -9294,10 +9294,10 @@
         <v>-0.1803426510369664</v>
       </c>
       <c r="J211" t="n">
+        <v>36718</v>
+      </c>
+      <c r="K211" t="n">
         <v>406104</v>
-      </c>
-      <c r="K211" t="n">
-        <v>449151024</v>
       </c>
       <c r="L211" t="n">
         <v>-0.001803426510369688</v>
@@ -9336,10 +9336,10 @@
         <v>0.9033423667569977</v>
       </c>
       <c r="J212" t="n">
+        <v>44618</v>
+      </c>
+      <c r="K212" t="n">
         <v>496151</v>
-      </c>
-      <c r="K212" t="n">
-        <v>551719912</v>
       </c>
       <c r="L212" t="n">
         <v>0.009033423667569984</v>
@@ -9378,10 +9378,10 @@
         <v>0.3581020590868481</v>
       </c>
       <c r="J213" t="n">
+        <v>45055</v>
+      </c>
+      <c r="K213" t="n">
         <v>503938</v>
-      </c>
-      <c r="K213" t="n">
-        <v>563654653</v>
       </c>
       <c r="L213" t="n">
         <v>0.0035810205908684</v>
@@ -9420,10 +9420,10 @@
         <v>-1.070472792149875</v>
       </c>
       <c r="J214" t="n">
+        <v>61096</v>
+      </c>
+      <c r="K214" t="n">
         <v>680915</v>
-      </c>
-      <c r="K214" t="n">
-        <v>759049996.25</v>
       </c>
       <c r="L214" t="n">
         <v>-0.01070472792149879</v>
@@ -9462,10 +9462,10 @@
         <v>-0.7213706041478817</v>
       </c>
       <c r="J215" t="n">
+        <v>65387</v>
+      </c>
+      <c r="K215" t="n">
         <v>722530</v>
-      </c>
-      <c r="K215" t="n">
-        <v>798395650</v>
       </c>
       <c r="L215" t="n">
         <v>-0.007213706041478862</v>
@@ -9504,10 +9504,10 @@
         <v>0.454132606721169</v>
       </c>
       <c r="J216" t="n">
+        <v>57094</v>
+      </c>
+      <c r="K216" t="n">
         <v>630034</v>
-      </c>
-      <c r="K216" t="n">
-        <v>694612485</v>
       </c>
       <c r="L216" t="n">
         <v>0.004541326067211582</v>
@@ -9546,10 +9546,10 @@
         <v>0.1808318264014428</v>
       </c>
       <c r="J217" t="n">
+        <v>72961</v>
+      </c>
+      <c r="K217" t="n">
         <v>806946</v>
-      </c>
-      <c r="K217" t="n">
-        <v>893894431.5</v>
       </c>
       <c r="L217" t="n">
         <v>0.001808318264014508</v>
@@ -9588,10 +9588,10 @@
         <v>-0.9025270758122712</v>
       </c>
       <c r="J218" t="n">
+        <v>76070</v>
+      </c>
+      <c r="K218" t="n">
         <v>839054</v>
-      </c>
-      <c r="K218" t="n">
-        <v>925057035</v>
       </c>
       <c r="L218" t="n">
         <v>-0.009025270758122761</v>
@@ -9630,10 +9630,10 @@
         <v>0.1821493624772275</v>
       </c>
       <c r="J219" t="n">
+        <v>58969</v>
+      </c>
+      <c r="K219" t="n">
         <v>648067</v>
-      </c>
-      <c r="K219" t="n">
-        <v>711901599.5</v>
       </c>
       <c r="L219" t="n">
         <v>0.001821493624772241</v>
@@ -9672,10 +9672,10 @@
         <v>0</v>
       </c>
       <c r="J220" t="n">
+        <v>53022</v>
+      </c>
+      <c r="K220" t="n">
         <v>582710</v>
-      </c>
-      <c r="K220" t="n">
-        <v>639961257.5</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -9714,10 +9714,10 @@
         <v>3.454545454545462</v>
       </c>
       <c r="J221" t="n">
+        <v>299540</v>
+      </c>
+      <c r="K221" t="n">
         <v>3401276</v>
-      </c>
-      <c r="K221" t="n">
-        <v>3874903683</v>
       </c>
       <c r="L221" t="n">
         <v>0.03454545454545466</v>
@@ -9756,10 +9756,10 @@
         <v>0.7029876977152906</v>
       </c>
       <c r="J222" t="n">
+        <v>146736</v>
+      </c>
+      <c r="K222" t="n">
         <v>1674259</v>
-      </c>
-      <c r="K222" t="n">
-        <v>1908655260</v>
       </c>
       <c r="L222" t="n">
         <v>0.007029876977152849</v>
@@ -9798,10 +9798,10 @@
         <v>0.5235602094240727</v>
       </c>
       <c r="J223" t="n">
+        <v>120124</v>
+      </c>
+      <c r="K223" t="n">
         <v>1378423</v>
-      </c>
-      <c r="K223" t="n">
-        <v>1581051181</v>
       </c>
       <c r="L223" t="n">
         <v>0.005235602094240788</v>
@@ -9840,10 +9840,10 @@
         <v>-0.2604166666666611</v>
       </c>
       <c r="J224" t="n">
+        <v>99108</v>
+      </c>
+      <c r="K224" t="n">
         <v>1139242</v>
-      </c>
-      <c r="K224" t="n">
-        <v>1311552352.5</v>
       </c>
       <c r="L224" t="n">
         <v>-0.00260416666666663</v>
@@ -9882,10 +9882,10 @@
         <v>-1.131418624891217</v>
       </c>
       <c r="J225" t="n">
+        <v>106421</v>
+      </c>
+      <c r="K225" t="n">
         <v>1216388</v>
-      </c>
-      <c r="K225" t="n">
-        <v>1388506902</v>
       </c>
       <c r="L225" t="n">
         <v>-0.01131418624891212</v>
@@ -9924,10 +9924,10 @@
         <v>0.08802816901408263</v>
       </c>
       <c r="J226" t="n">
+        <v>82406</v>
+      </c>
+      <c r="K226" t="n">
         <v>936958</v>
-      </c>
-      <c r="K226" t="n">
-        <v>1064150048.5</v>
       </c>
       <c r="L226" t="n">
         <v>0.0008802816901407606</v>
@@ -9966,10 +9966,10 @@
         <v>-0.615655233069468</v>
       </c>
       <c r="J227" t="n">
+        <v>70567</v>
+      </c>
+      <c r="K227" t="n">
         <v>798820</v>
-      </c>
-      <c r="K227" t="n">
-        <v>905861880</v>
       </c>
       <c r="L227" t="n">
         <v>-0.006156552330694676</v>
@@ -10008,10 +10008,10 @@
         <v>-0.1769911504424898</v>
       </c>
       <c r="J228" t="n">
+        <v>82576</v>
+      </c>
+      <c r="K228" t="n">
         <v>931865</v>
-      </c>
-      <c r="K228" t="n">
-        <v>1049279990</v>
       </c>
       <c r="L228" t="n">
         <v>-0.001769911504424848</v>
@@ -10050,10 +10050,10 @@
         <v>-0.265957446808505</v>
       </c>
       <c r="J229" t="n">
+        <v>91348</v>
+      </c>
+      <c r="K229" t="n">
         <v>1029038</v>
-      </c>
-      <c r="K229" t="n">
-        <v>1160240345</v>
       </c>
       <c r="L229" t="n">
         <v>-0.002659574468085069</v>
@@ -10092,10 +10092,10 @@
         <v>-0.9777777777777727</v>
       </c>
       <c r="J230" t="n">
+        <v>90931</v>
+      </c>
+      <c r="K230" t="n">
         <v>1017974</v>
-      </c>
-      <c r="K230" t="n">
-        <v>1139621893</v>
       </c>
       <c r="L230" t="n">
         <v>-0.009777777777777774</v>
@@ -10134,10 +10134,10 @@
         <v>-0.8078994614003578</v>
       </c>
       <c r="J231" t="n">
+        <v>71597</v>
+      </c>
+      <c r="K231" t="n">
         <v>794368</v>
-      </c>
-      <c r="K231" t="n">
-        <v>881549888</v>
       </c>
       <c r="L231" t="n">
         <v>-0.008078994614003632</v>
@@ -10176,10 +10176,10 @@
         <v>-0.542986425339371</v>
       </c>
       <c r="J232" t="n">
+        <v>88452</v>
+      </c>
+      <c r="K232" t="n">
         <v>974742</v>
-      </c>
-      <c r="K232" t="n">
-        <v>1074896740.5</v>
       </c>
       <c r="L232" t="n">
         <v>-0.005429864253393757</v>
@@ -10218,10 +10218,10 @@
         <v>-1.182893539581445</v>
       </c>
       <c r="J233" t="n">
+        <v>78495</v>
+      </c>
+      <c r="K233" t="n">
         <v>856382</v>
-      </c>
-      <c r="K233" t="n">
-        <v>933670475.5</v>
       </c>
       <c r="L233" t="n">
         <v>-0.01182893539581442</v>
@@ -10260,10 +10260,10 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
+        <v>73170</v>
+      </c>
+      <c r="K234" t="n">
         <v>793529</v>
-      </c>
-      <c r="K234" t="n">
-        <v>861772494</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>-0.8287292817679546</v>
       </c>
       <c r="J235" t="n">
+        <v>69129</v>
+      </c>
+      <c r="K235" t="n">
         <v>747632</v>
-      </c>
-      <c r="K235" t="n">
-        <v>808750916</v>
       </c>
       <c r="L235" t="n">
         <v>-0.008287292817679592</v>
@@ -10344,10 +10344,10 @@
         <v>-0.6499535747446638</v>
       </c>
       <c r="J236" t="n">
+        <v>103372</v>
+      </c>
+      <c r="K236" t="n">
         <v>1110211</v>
-      </c>
-      <c r="K236" t="n">
-        <v>1192644166.75</v>
       </c>
       <c r="L236" t="n">
         <v>-0.006499535747446661</v>
@@ -10386,10 +10386,10 @@
         <v>-0.1869158878504633</v>
       </c>
       <c r="J237" t="n">
+        <v>89255</v>
+      </c>
+      <c r="K237" t="n">
         <v>954133</v>
-      </c>
-      <c r="K237" t="n">
-        <v>1019968177</v>
       </c>
       <c r="L237" t="n">
         <v>-0.001869158878504584</v>
@@ -10428,10 +10428,10 @@
         <v>0</v>
       </c>
       <c r="J238" t="n">
+        <v>62088</v>
+      </c>
+      <c r="K238" t="n">
         <v>663103</v>
-      </c>
-      <c r="K238" t="n">
-        <v>708857107</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -10470,10 +10470,10 @@
         <v>1.029962546816474</v>
       </c>
       <c r="J239" t="n">
+        <v>77893</v>
+      </c>
+      <c r="K239" t="n">
         <v>837347</v>
-      </c>
-      <c r="K239" t="n">
-        <v>899938688.25</v>
       </c>
       <c r="L239" t="n">
         <v>0.01029962546816465</v>
@@ -10512,10 +10512,10 @@
         <v>-0.2780352177942481</v>
       </c>
       <c r="J240" t="n">
+        <v>78042</v>
+      </c>
+      <c r="K240" t="n">
         <v>839727</v>
-      </c>
-      <c r="K240" t="n">
-        <v>904595910.75</v>
       </c>
       <c r="L240" t="n">
         <v>-0.00278035217794248</v>
@@ -10554,10 +10554,10 @@
         <v>-0.9293680297397737</v>
       </c>
       <c r="J241" t="n">
+        <v>84100</v>
+      </c>
+      <c r="K241" t="n">
         <v>900711</v>
-      </c>
-      <c r="K241" t="n">
-        <v>964661481</v>
       </c>
       <c r="L241" t="n">
         <v>-0.009293680297397744</v>
@@ -10596,10 +10596,10 @@
         <v>2.532833020637895</v>
       </c>
       <c r="J242" t="n">
+        <v>129691</v>
+      </c>
+      <c r="K242" t="n">
         <v>1399368</v>
-      </c>
-      <c r="K242" t="n">
-        <v>1508868546</v>
       </c>
       <c r="L242" t="n">
         <v>0.02532833020637892</v>
@@ -10638,10 +10638,10 @@
         <v>0.5489478499542589</v>
       </c>
       <c r="J243" t="n">
+        <v>87218</v>
+      </c>
+      <c r="K243" t="n">
         <v>954596</v>
-      </c>
-      <c r="K243" t="n">
-        <v>1042657481</v>
       </c>
       <c r="L243" t="n">
         <v>0.005489478499542511</v>
@@ -10680,10 +10680,10 @@
         <v>0.8189262966333016</v>
       </c>
       <c r="J244" t="n">
+        <v>80275</v>
+      </c>
+      <c r="K244" t="n">
         <v>885428</v>
-      </c>
-      <c r="K244" t="n">
-        <v>976184370</v>
       </c>
       <c r="L244" t="n">
         <v>0.008189262966332933</v>
@@ -10722,10 +10722,10 @@
         <v>-0.8122743682310456</v>
       </c>
       <c r="J245" t="n">
+        <v>74957</v>
+      </c>
+      <c r="K245" t="n">
         <v>825272</v>
-      </c>
-      <c r="K245" t="n">
-        <v>907799200</v>
       </c>
       <c r="L245" t="n">
         <v>-0.008122743682310474</v>
@@ -10764,10 +10764,10 @@
         <v>-1.546860782529571</v>
       </c>
       <c r="J246" t="n">
+        <v>80007</v>
+      </c>
+      <c r="K246" t="n">
         <v>869271</v>
-      </c>
-      <c r="K246" t="n">
-        <v>944680259.25</v>
       </c>
       <c r="L246" t="n">
         <v>-0.01546860782529569</v>
@@ -10806,10 +10806,10 @@
         <v>1.478743068391868</v>
       </c>
       <c r="J247" t="n">
+        <v>92022</v>
+      </c>
+      <c r="K247" t="n">
         <v>1003503</v>
-      </c>
-      <c r="K247" t="n">
-        <v>1095574400.25</v>
       </c>
       <c r="L247" t="n">
         <v>0.01478743068391863</v>
@@ -10848,10 +10848,10 @@
         <v>0.4553734061930685</v>
       </c>
       <c r="J248" t="n">
+        <v>99175</v>
+      </c>
+      <c r="K248" t="n">
         <v>1090926</v>
-      </c>
-      <c r="K248" t="n">
-        <v>1201654989</v>
       </c>
       <c r="L248" t="n">
         <v>0.004553734061930603</v>
@@ -10890,10 +10890,10 @@
         <v>0.9066183136899495</v>
       </c>
       <c r="J249" t="n">
+        <v>103855</v>
+      </c>
+      <c r="K249" t="n">
         <v>1149672</v>
-      </c>
-      <c r="K249" t="n">
-        <v>1272974322</v>
       </c>
       <c r="L249" t="n">
         <v>0.009066183136899442</v>
@@ -10932,10 +10932,10 @@
         <v>1.707097933513023</v>
       </c>
       <c r="J250" t="n">
+        <v>137845</v>
+      </c>
+      <c r="K250" t="n">
         <v>1543176</v>
-      </c>
-      <c r="K250" t="n">
-        <v>1728742914</v>
       </c>
       <c r="L250" t="n">
         <v>0.01707097933513024</v>
@@ -10974,10 +10974,10 @@
         <v>-0.1766784452296782</v>
       </c>
       <c r="J251" t="n">
+        <v>102230</v>
+      </c>
+      <c r="K251" t="n">
         <v>1156222</v>
-      </c>
-      <c r="K251" t="n">
-        <v>1308265193</v>
       </c>
       <c r="L251" t="n">
         <v>-0.001766784452296832</v>
@@ -11016,10 +11016,10 @@
         <v>-0.530973451327438</v>
       </c>
       <c r="J252" t="n">
+        <v>182766</v>
+      </c>
+      <c r="K252" t="n">
         <v>2032355</v>
-      </c>
-      <c r="K252" t="n">
-        <v>2254389783.75</v>
       </c>
       <c r="L252" t="n">
         <v>-0.005309734513274433</v>
@@ -11058,10 +11058,10 @@
         <v>-1.601423487544481</v>
       </c>
       <c r="J253" t="n">
+        <v>138420</v>
+      </c>
+      <c r="K253" t="n">
         <v>1541305</v>
-      </c>
-      <c r="K253" t="n">
-        <v>1713160507.5</v>
       </c>
       <c r="L253" t="n">
         <v>-0.01601423487544484</v>
@@ -11100,10 +11100,10 @@
         <v>-1.084990958408689</v>
       </c>
       <c r="J254" t="n">
+        <v>85740</v>
+      </c>
+      <c r="K254" t="n">
         <v>942708</v>
-      </c>
-      <c r="K254" t="n">
-        <v>1037450154</v>
       </c>
       <c r="L254" t="n">
         <v>-0.01084990958408694</v>
@@ -11142,10 +11142,10 @@
         <v>-1.462522851919563</v>
       </c>
       <c r="J255" t="n">
+        <v>88812</v>
+      </c>
+      <c r="K255" t="n">
         <v>965828</v>
-      </c>
-      <c r="K255" t="n">
-        <v>1050096493</v>
       </c>
       <c r="L255" t="n">
         <v>-0.01462522851919568</v>
@@ -11184,10 +11184,10 @@
         <v>-2.411873840445268</v>
       </c>
       <c r="J256" t="n">
+        <v>134233</v>
+      </c>
+      <c r="K256" t="n">
         <v>1426893</v>
-      </c>
-      <c r="K256" t="n">
-        <v>1517857428.75</v>
       </c>
       <c r="L256" t="n">
         <v>-0.02411873840445267</v>
@@ -11226,10 +11226,10 @@
         <v>1.235741444866927</v>
       </c>
       <c r="J257" t="n">
+        <v>119539</v>
+      </c>
+      <c r="K257" t="n">
         <v>1265317</v>
-      </c>
-      <c r="K257" t="n">
-        <v>1336807410.5</v>
       </c>
       <c r="L257" t="n">
         <v>0.01235741444866933</v>
@@ -11268,10 +11268,10 @@
         <v>0.5633802816901454</v>
       </c>
       <c r="J258" t="n">
+        <v>111480</v>
+      </c>
+      <c r="K258" t="n">
         <v>1190604</v>
-      </c>
-      <c r="K258" t="n">
-        <v>1276922790</v>
       </c>
       <c r="L258" t="n">
         <v>0.005633802816901401</v>
@@ -11310,10 +11310,10 @@
         <v>-1.867413632119524</v>
       </c>
       <c r="J259" t="n">
+        <v>106262</v>
+      </c>
+      <c r="K259" t="n">
         <v>1125841</v>
-      </c>
-      <c r="K259" t="n">
-        <v>1195643142</v>
       </c>
       <c r="L259" t="n">
         <v>-0.01867413632119519</v>
@@ -11352,10 +11352,10 @@
         <v>-0.8563273073263546</v>
       </c>
       <c r="J260" t="n">
+        <v>103782</v>
+      </c>
+      <c r="K260" t="n">
         <v>1083999</v>
-      </c>
-      <c r="K260" t="n">
-        <v>1135217952.75</v>
       </c>
       <c r="L260" t="n">
         <v>-0.008563273073263544</v>
@@ -11394,10 +11394,10 @@
         <v>-1.823416506717845</v>
       </c>
       <c r="J261" t="n">
+        <v>119756</v>
+      </c>
+      <c r="K261" t="n">
         <v>1236482</v>
-      </c>
-      <c r="K261" t="n">
-        <v>1276976785.5</v>
       </c>
       <c r="L261" t="n">
         <v>-0.01823416506717845</v>
@@ -11436,10 +11436,10 @@
         <v>0.09775171065493438</v>
       </c>
       <c r="J262" t="n">
+        <v>109887</v>
+      </c>
+      <c r="K262" t="n">
         <v>1124140</v>
-      </c>
-      <c r="K262" t="n">
-        <v>1146622800</v>
       </c>
       <c r="L262" t="n">
         <v>0.0009775171065493637</v>
@@ -11478,10 +11478,10 @@
         <v>-1.855468749999995</v>
       </c>
       <c r="J263" t="n">
+        <v>109655</v>
+      </c>
+      <c r="K263" t="n">
         <v>1111353</v>
-      </c>
-      <c r="K263" t="n">
-        <v>1126078427.25</v>
       </c>
       <c r="L263" t="n">
         <v>-0.0185546875</v>
@@ -11520,10 +11520,10 @@
         <v>1.094527363184074</v>
       </c>
       <c r="J264" t="n">
+        <v>89747</v>
+      </c>
+      <c r="K264" t="n">
         <v>906890</v>
-      </c>
-      <c r="K264" t="n">
-        <v>915505455</v>
       </c>
       <c r="L264" t="n">
         <v>0.01094527363184072</v>
@@ -11562,10 +11562,10 @@
         <v>1.181102362204717</v>
       </c>
       <c r="J265" t="n">
+        <v>98120</v>
+      </c>
+      <c r="K265" t="n">
         <v>1004749</v>
-      </c>
-      <c r="K265" t="n">
-        <v>1030118912.25</v>
       </c>
       <c r="L265" t="n">
         <v>0.01181102362204722</v>
@@ -11604,10 +11604,10 @@
         <v>0.09727626459143762</v>
       </c>
       <c r="J266" t="n">
+        <v>83900</v>
+      </c>
+      <c r="K266" t="n">
         <v>863327</v>
-      </c>
-      <c r="K266" t="n">
-        <v>888363483</v>
       </c>
       <c r="L266" t="n">
         <v>0.0009727626459143934</v>
@@ -11716,10 +11716,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>204618</v>
+      </c>
+      <c r="K2" t="n">
         <v>2192480</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2354175400</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -11756,10 +11756,10 @@
         <v>0.2764976958525451</v>
       </c>
       <c r="J3" t="n">
+        <v>107448</v>
+      </c>
+      <c r="K3" t="n">
         <v>1167960</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1269572520</v>
       </c>
       <c r="L3" t="n">
         <v>0.0027649769585254</v>
@@ -11798,10 +11798,10 @@
         <v>-1.562499999999999</v>
       </c>
       <c r="J4" t="n">
+        <v>107887</v>
+      </c>
+      <c r="K4" t="n">
         <v>1166803</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1262480846</v>
       </c>
       <c r="L4" t="n">
         <v>-0.015625</v>
@@ -11840,10 +11840,10 @@
         <v>0.2801120448179212</v>
       </c>
       <c r="J5" t="n">
+        <v>63534</v>
+      </c>
+      <c r="K5" t="n">
         <v>682353</v>
-      </c>
-      <c r="K5" t="n">
-        <v>734041239.75</v>
       </c>
       <c r="L5" t="n">
         <v>0.002801120448179262</v>
@@ -11882,10 +11882,10 @@
         <v>0.09310986964618051</v>
       </c>
       <c r="J6" t="n">
+        <v>71864</v>
+      </c>
+      <c r="K6" t="n">
         <v>773255</v>
-      </c>
-      <c r="K6" t="n">
-        <v>831249125</v>
       </c>
       <c r="L6" t="n">
         <v>0.0009310986964619072</v>
@@ -11924,10 +11924,10 @@
         <v>0.9302325581395315</v>
       </c>
       <c r="J7" t="n">
+        <v>132173</v>
+      </c>
+      <c r="K7" t="n">
         <v>1428132</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1545595857</v>
       </c>
       <c r="L7" t="n">
         <v>0.009302325581395321</v>
@@ -11966,10 +11966,10 @@
         <v>0.3686635944700546</v>
       </c>
       <c r="J8" t="n">
+        <v>100659</v>
+      </c>
+      <c r="K8" t="n">
         <v>1094667</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1191818696.25</v>
       </c>
       <c r="L8" t="n">
         <v>0.003686635944700534</v>
@@ -12008,10 +12008,10 @@
         <v>1.744719926538104</v>
       </c>
       <c r="J9" t="n">
+        <v>117080</v>
+      </c>
+      <c r="K9" t="n">
         <v>1290220</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1421177330</v>
       </c>
       <c r="L9" t="n">
         <v>0.01744719926538107</v>
@@ -12050,10 +12050,10 @@
         <v>-0.9025270758122712</v>
       </c>
       <c r="J10" t="n">
+        <v>99319</v>
+      </c>
+      <c r="K10" t="n">
         <v>1095494</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1209425376</v>
       </c>
       <c r="L10" t="n">
         <v>-0.009025270758122761</v>
@@ -12092,10 +12092,10 @@
         <v>1.91256830601092</v>
       </c>
       <c r="J11" t="n">
+        <v>105996</v>
+      </c>
+      <c r="K11" t="n">
         <v>1174438</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1300102866</v>
       </c>
       <c r="L11" t="n">
         <v>0.0191256830601092</v>
@@ -12134,10 +12134,10 @@
         <v>-0.2680965147453026</v>
       </c>
       <c r="J12" t="n">
+        <v>79644</v>
+      </c>
+      <c r="K12" t="n">
         <v>890027</v>
-      </c>
-      <c r="K12" t="n">
-        <v>995495199.5</v>
       </c>
       <c r="L12" t="n">
         <v>-0.002680965147452974</v>
@@ -12176,10 +12176,10 @@
         <v>0.08960573476702319</v>
       </c>
       <c r="J13" t="n">
+        <v>61165</v>
+      </c>
+      <c r="K13" t="n">
         <v>683521</v>
-      </c>
-      <c r="K13" t="n">
-        <v>762467675.5</v>
       </c>
       <c r="L13" t="n">
         <v>0.0008960573476701761</v>
@@ -12218,10 +12218,10 @@
         <v>-0.6266786034019721</v>
       </c>
       <c r="J14" t="n">
+        <v>74775</v>
+      </c>
+      <c r="K14" t="n">
         <v>832247</v>
-      </c>
-      <c r="K14" t="n">
-        <v>925666725.75</v>
       </c>
       <c r="L14" t="n">
         <v>-0.006266786034019756</v>
@@ -12260,10 +12260,10 @@
         <v>1.261261261261266</v>
       </c>
       <c r="J15" t="n">
+        <v>117207</v>
+      </c>
+      <c r="K15" t="n">
         <v>1309198</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1462046866.5</v>
       </c>
       <c r="L15" t="n">
         <v>0.01261261261261271</v>
@@ -12302,10 +12302,10 @@
         <v>0.8007117437722406</v>
       </c>
       <c r="J16" t="n">
+        <v>123263</v>
+      </c>
+      <c r="K16" t="n">
         <v>1389170</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1562121665</v>
       </c>
       <c r="L16" t="n">
         <v>0.008007117437722311</v>
@@ -12344,10 +12344,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>115645</v>
+      </c>
+      <c r="K17" t="n">
         <v>1308525</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1481250300</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -12386,10 +12386,10 @@
         <v>1.147396293027368</v>
       </c>
       <c r="J18" t="n">
+        <v>147004</v>
+      </c>
+      <c r="K18" t="n">
         <v>1675116</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1905444450</v>
       </c>
       <c r="L18" t="n">
         <v>0.01147396293027358</v>
@@ -12428,10 +12428,10 @@
         <v>3.054101221640485</v>
       </c>
       <c r="J19" t="n">
+        <v>186980</v>
+      </c>
+      <c r="K19" t="n">
         <v>2174578</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2530665147.5</v>
       </c>
       <c r="L19" t="n">
         <v>0.03054101221640493</v>
@@ -12470,10 +12470,10 @@
         <v>-1.778154106689253</v>
       </c>
       <c r="J20" t="n">
+        <v>203475</v>
+      </c>
+      <c r="K20" t="n">
         <v>2377600</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2786547200</v>
       </c>
       <c r="L20" t="n">
         <v>-0.01778154106689256</v>
@@ -12512,10 +12512,10 @@
         <v>-1.120689655172405</v>
       </c>
       <c r="J21" t="n">
+        <v>130797</v>
+      </c>
+      <c r="K21" t="n">
         <v>1504820</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1728285770</v>
       </c>
       <c r="L21" t="n">
         <v>-0.01120689655172402</v>
@@ -12554,10 +12554,10 @@
         <v>2.00523103748909</v>
       </c>
       <c r="J22" t="n">
+        <v>116955</v>
+      </c>
+      <c r="K22" t="n">
         <v>1354341</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1569342633.75</v>
       </c>
       <c r="L22" t="n">
         <v>0.02005231037489086</v>
@@ -12596,10 +12596,10 @@
         <v>0.1709401709401825</v>
       </c>
       <c r="J23" t="n">
+        <v>102468</v>
+      </c>
+      <c r="K23" t="n">
         <v>1200412</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1406582761</v>
       </c>
       <c r="L23" t="n">
         <v>0.001709401709401925</v>
@@ -12638,10 +12638,10 @@
         <v>0.2559726962457283</v>
       </c>
       <c r="J24" t="n">
+        <v>67639</v>
+      </c>
+      <c r="K24" t="n">
         <v>794086</v>
-      </c>
-      <c r="K24" t="n">
-        <v>932654007</v>
       </c>
       <c r="L24" t="n">
         <v>0.00255972696245732</v>
@@ -12680,10 +12680,10 @@
         <v>2.127659574468085</v>
       </c>
       <c r="J25" t="n">
+        <v>149502</v>
+      </c>
+      <c r="K25" t="n">
         <v>1775333</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2111314770.25</v>
       </c>
       <c r="L25" t="n">
         <v>0.02127659574468077</v>
@@ -12722,10 +12722,10 @@
         <v>1.499999999999998</v>
       </c>
       <c r="J26" t="n">
+        <v>123690</v>
+      </c>
+      <c r="K26" t="n">
         <v>1495407</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1809442470</v>
       </c>
       <c r="L26" t="n">
         <v>0.0149999999999999</v>
@@ -12764,10 +12764,10 @@
         <v>-0.7389162561576343</v>
       </c>
       <c r="J27" t="n">
+        <v>90015</v>
+      </c>
+      <c r="K27" t="n">
         <v>1090986</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1323638764.5</v>
       </c>
       <c r="L27" t="n">
         <v>-0.00738916256157629</v>
@@ -12806,10 +12806,10 @@
         <v>1.240694789081889</v>
       </c>
       <c r="J28" t="n">
+        <v>99256</v>
+      </c>
+      <c r="K28" t="n">
         <v>1205963</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1467053989.5</v>
       </c>
       <c r="L28" t="n">
         <v>0.01240694789081886</v>
@@ -12848,10 +12848,10 @@
         <v>2.777777777777777</v>
       </c>
       <c r="J29" t="n">
+        <v>200114</v>
+      </c>
+      <c r="K29" t="n">
         <v>2481416</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3084400088</v>
       </c>
       <c r="L29" t="n">
         <v>0.02777777777777768</v>
@@ -12890,10 +12890,10 @@
         <v>-2.14626391096979</v>
       </c>
       <c r="J30" t="n">
+        <v>196285</v>
+      </c>
+      <c r="K30" t="n">
         <v>2443744</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3047959704</v>
       </c>
       <c r="L30" t="n">
         <v>-0.02146263910969792</v>
@@ -12932,10 +12932,10 @@
         <v>0.5686433793663711</v>
       </c>
       <c r="J31" t="n">
+        <v>151959</v>
+      </c>
+      <c r="K31" t="n">
         <v>1872896</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2316772352</v>
       </c>
       <c r="L31" t="n">
         <v>0.005686433793663737</v>
@@ -12974,10 +12974,10 @@
         <v>-2.019386106623586</v>
       </c>
       <c r="J32" t="n">
+        <v>147678</v>
+      </c>
+      <c r="K32" t="n">
         <v>1810531</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2221068904.25</v>
       </c>
       <c r="L32" t="n">
         <v>-0.02019386106623589</v>
@@ -13016,10 +13016,10 @@
         <v>-0.7419620774938304</v>
       </c>
       <c r="J33" t="n">
+        <v>159525</v>
+      </c>
+      <c r="K33" t="n">
         <v>1927864</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2324522018</v>
       </c>
       <c r="L33" t="n">
         <v>-0.007419620774938296</v>
@@ -13058,10 +13058,10 @@
         <v>-0.4152823920265692</v>
       </c>
       <c r="J34" t="n">
+        <v>78720</v>
+      </c>
+      <c r="K34" t="n">
         <v>944641</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1134513841</v>
       </c>
       <c r="L34" t="n">
         <v>-0.004152823920265725</v>
@@ -13100,10 +13100,10 @@
         <v>0.9174311926605456</v>
       </c>
       <c r="J35" t="n">
+        <v>102919</v>
+      </c>
+      <c r="K35" t="n">
         <v>1241206</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1497825340.5</v>
       </c>
       <c r="L35" t="n">
         <v>0.00917431192660545</v>
@@ -13142,10 +13142,10 @@
         <v>-0.7438016528925608</v>
       </c>
       <c r="J36" t="n">
+        <v>89732</v>
+      </c>
+      <c r="K36" t="n">
         <v>1079027</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1297799724.25</v>
       </c>
       <c r="L36" t="n">
         <v>-0.007438016528925617</v>
@@ -13184,10 +13184,10 @@
         <v>-0.9991673605328828</v>
       </c>
       <c r="J37" t="n">
+        <v>162012</v>
+      </c>
+      <c r="K37" t="n">
         <v>1935229</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2303406317.25</v>
       </c>
       <c r="L37" t="n">
         <v>-0.009991673605328821</v>
@@ -13226,10 +13226,10 @@
         <v>0.3364171572750139</v>
       </c>
       <c r="J38" t="n">
+        <v>115218</v>
+      </c>
+      <c r="K38" t="n">
         <v>1370520</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1633317210</v>
       </c>
       <c r="L38" t="n">
         <v>0.003364171572750152</v>
@@ -13268,10 +13268,10 @@
         <v>-1.508801341156745</v>
       </c>
       <c r="J39" t="n">
+        <v>165486</v>
+      </c>
+      <c r="K39" t="n">
         <v>1959351</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2318891908.5</v>
       </c>
       <c r="L39" t="n">
         <v>-0.0150880134115674</v>
@@ -13310,10 +13310,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
+        <v>94401</v>
+      </c>
+      <c r="K40" t="n">
         <v>1108267</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1303876125.5</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -13352,10 +13352,10 @@
         <v>0.9361702127659527</v>
       </c>
       <c r="J41" t="n">
+        <v>104891</v>
+      </c>
+      <c r="K41" t="n">
         <v>1238243</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1462984104.5</v>
       </c>
       <c r="L41" t="n">
         <v>0.009361702127659521</v>
@@ -13394,10 +13394,10 @@
         <v>-1.01180438448566</v>
       </c>
       <c r="J42" t="n">
+        <v>85832</v>
+      </c>
+      <c r="K42" t="n">
         <v>1012818</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1196391262.5</v>
       </c>
       <c r="L42" t="n">
         <v>-0.01011804384485659</v>
@@ -13436,10 +13436,10 @@
         <v>1.277683134582627</v>
       </c>
       <c r="J43" t="n">
+        <v>145107</v>
+      </c>
+      <c r="K43" t="n">
         <v>1715164</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2033326922</v>
       </c>
       <c r="L43" t="n">
         <v>0.0127768313458263</v>
@@ -13478,10 +13478,10 @@
         <v>-2.186711522287635</v>
       </c>
       <c r="J44" t="n">
+        <v>143592</v>
+      </c>
+      <c r="K44" t="n">
         <v>1690081</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1990492897.75</v>
       </c>
       <c r="L44" t="n">
         <v>-0.02186711522287632</v>
@@ -13520,10 +13520,10 @@
         <v>0.4299226139294835</v>
       </c>
       <c r="J45" t="n">
+        <v>86808</v>
+      </c>
+      <c r="K45" t="n">
         <v>1012187</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1179197855</v>
       </c>
       <c r="L45" t="n">
         <v>0.004299226139294898</v>
@@ -13562,10 +13562,10 @@
         <v>0.1712328767123251</v>
       </c>
       <c r="J46" t="n">
+        <v>88491</v>
+      </c>
+      <c r="K46" t="n">
         <v>1032690</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1206440092.5</v>
       </c>
       <c r="L46" t="n">
         <v>0.001712328767123239</v>
@@ -13604,10 +13604,10 @@
         <v>1.452991452991452</v>
       </c>
       <c r="J47" t="n">
+        <v>96061</v>
+      </c>
+      <c r="K47" t="n">
         <v>1132078</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1334436942.5</v>
       </c>
       <c r="L47" t="n">
         <v>0.01452991452991448</v>
@@ -13646,10 +13646,10 @@
         <v>-0.08424599831507824</v>
       </c>
       <c r="J48" t="n">
+        <v>58192</v>
+      </c>
+      <c r="K48" t="n">
         <v>690448</v>
-      </c>
-      <c r="K48" t="n">
-        <v>819043940</v>
       </c>
       <c r="L48" t="n">
         <v>-0.0008424599831508006</v>
@@ -13688,10 +13688,10 @@
         <v>0.08431703204047038</v>
       </c>
       <c r="J49" t="n">
+        <v>60907</v>
+      </c>
+      <c r="K49" t="n">
         <v>722053</v>
-      </c>
-      <c r="K49" t="n">
-        <v>856174344.75</v>
       </c>
       <c r="L49" t="n">
         <v>0.0008431703204045959</v>
@@ -13730,10 +13730,10 @@
         <v>-0.5897219882055477</v>
       </c>
       <c r="J50" t="n">
+        <v>70084</v>
+      </c>
+      <c r="K50" t="n">
         <v>829796</v>
-      </c>
-      <c r="K50" t="n">
-        <v>983308260</v>
       </c>
       <c r="L50" t="n">
         <v>-0.005897219882055493</v>
@@ -13772,10 +13772,10 @@
         <v>-0.847457627118656</v>
       </c>
       <c r="J51" t="n">
+        <v>79519</v>
+      </c>
+      <c r="K51" t="n">
         <v>934353</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1097631186.75</v>
       </c>
       <c r="L51" t="n">
         <v>-0.008474576271186529</v>
@@ -13814,10 +13814,10 @@
         <v>0.2564102564102661</v>
       </c>
       <c r="J52" t="n">
+        <v>58050</v>
+      </c>
+      <c r="K52" t="n">
         <v>680056</v>
-      </c>
-      <c r="K52" t="n">
-        <v>797875702</v>
       </c>
       <c r="L52" t="n">
         <v>0.002564102564102555</v>
@@ -13856,10 +13856,10 @@
         <v>-0.5967604433077602</v>
       </c>
       <c r="J53" t="n">
+        <v>95588</v>
+      </c>
+      <c r="K53" t="n">
         <v>1119813</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1311860929.5</v>
       </c>
       <c r="L53" t="n">
         <v>-0.005967604433077645</v>
@@ -13898,10 +13898,10 @@
         <v>-0.514579759862783</v>
       </c>
       <c r="J54" t="n">
+        <v>106664</v>
+      </c>
+      <c r="K54" t="n">
         <v>1241041</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1445812765</v>
       </c>
       <c r="L54" t="n">
         <v>-0.005145797598627877</v>
@@ -13940,10 +13940,10 @@
         <v>-1.034482758620683</v>
       </c>
       <c r="J55" t="n">
+        <v>168629</v>
+      </c>
+      <c r="K55" t="n">
         <v>1948503</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2244675456</v>
       </c>
       <c r="L55" t="n">
         <v>-0.01034482758620681</v>
@@ -13982,10 +13982,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>108026</v>
+      </c>
+      <c r="K56" t="n">
         <v>1239058</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1422438584</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -14024,10 +14024,10 @@
         <v>-0.1742160278745607</v>
       </c>
       <c r="J57" t="n">
+        <v>77775</v>
+      </c>
+      <c r="K57" t="n">
         <v>892860</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1024556850</v>
       </c>
       <c r="L57" t="n">
         <v>-0.00174216027874563</v>
@@ -14066,10 +14066,10 @@
         <v>0.0872600349040121</v>
       </c>
       <c r="J58" t="n">
+        <v>91473</v>
+      </c>
+      <c r="K58" t="n">
         <v>1048739</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1201592709.25</v>
       </c>
       <c r="L58" t="n">
         <v>0.0008726003490400203</v>
@@ -14108,10 +14108,10 @@
         <v>0.6974716652136013</v>
       </c>
       <c r="J59" t="n">
+        <v>105862</v>
+      </c>
+      <c r="K59" t="n">
         <v>1217418</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1400639409</v>
       </c>
       <c r="L59" t="n">
         <v>0.006974716652136115</v>
@@ -14150,10 +14150,10 @@
         <v>-0.7792207792207779</v>
       </c>
       <c r="J60" t="n">
+        <v>142917</v>
+      </c>
+      <c r="K60" t="n">
         <v>1644260</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1889254740</v>
       </c>
       <c r="L60" t="n">
         <v>-0.007792207792207795</v>
@@ -14192,10 +14192,10 @@
         <v>3.403141361256533</v>
       </c>
       <c r="J61" t="n">
+        <v>260598</v>
+      </c>
+      <c r="K61" t="n">
         <v>3045088</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3562752960</v>
       </c>
       <c r="L61" t="n">
         <v>0.03403141361256523</v>
@@ -14234,10 +14234,10 @@
         <v>-0.7594936708860748</v>
       </c>
       <c r="J62" t="n">
+        <v>117204</v>
+      </c>
+      <c r="K62" t="n">
         <v>1383599</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1632992719.75</v>
       </c>
       <c r="L62" t="n">
         <v>-0.0075949367088608</v>
@@ -14276,10 +14276,10 @@
         <v>-2.551020408163256</v>
       </c>
       <c r="J63" t="n">
+        <v>160487</v>
+      </c>
+      <c r="K63" t="n">
         <v>1860050</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2157192987.5</v>
       </c>
       <c r="L63" t="n">
         <v>-0.02551020408163251</v>
@@ -14318,10 +14318,10 @@
         <v>0.1745200698080242</v>
       </c>
       <c r="J64" t="n">
+        <v>143978</v>
+      </c>
+      <c r="K64" t="n">
         <v>1653588</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1896665436</v>
       </c>
       <c r="L64" t="n">
         <v>0.001745200698080263</v>
@@ -14360,10 +14360,10 @@
         <v>-0.2613240418118566</v>
       </c>
       <c r="J65" t="n">
+        <v>157653</v>
+      </c>
+      <c r="K65" t="n">
         <v>1805126</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2073638492.5</v>
       </c>
       <c r="L65" t="n">
         <v>-0.002613240418118612</v>
@@ -14402,10 +14402,10 @@
         <v>-1.397379912663757</v>
       </c>
       <c r="J66" t="n">
+        <v>163453</v>
+      </c>
+      <c r="K66" t="n">
         <v>1858459</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2111209424</v>
       </c>
       <c r="L66" t="n">
         <v>-0.01397379912663754</v>
@@ -14444,10 +14444,10 @@
         <v>0.7971656333038233</v>
       </c>
       <c r="J67" t="n">
+        <v>131924</v>
+      </c>
+      <c r="K67" t="n">
         <v>1492716</v>
-      </c>
-      <c r="K67" t="n">
-        <v>1689008154</v>
       </c>
       <c r="L67" t="n">
         <v>0.007971656333038313</v>
@@ -14486,10 +14486,10 @@
         <v>-2.021089630931462</v>
       </c>
       <c r="J68" t="n">
+        <v>121370</v>
+      </c>
+      <c r="K68" t="n">
         <v>1367232</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1540870464</v>
       </c>
       <c r="L68" t="n">
         <v>-0.02021089630931461</v>
@@ -14528,10 +14528,10 @@
         <v>-0.0896860986547066</v>
       </c>
       <c r="J69" t="n">
+        <v>116170</v>
+      </c>
+      <c r="K69" t="n">
         <v>1295300</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1440049775</v>
       </c>
       <c r="L69" t="n">
         <v>-0.0008968609865470656</v>
@@ -14570,10 +14570,10 @@
         <v>-0.1795332136445363</v>
       </c>
       <c r="J70" t="n">
+        <v>73677</v>
+      </c>
+      <c r="K70" t="n">
         <v>819662</v>
-      </c>
-      <c r="K70" t="n">
-        <v>910234651</v>
       </c>
       <c r="L70" t="n">
         <v>-0.001795332136445338</v>
@@ -14612,10 +14612,10 @@
         <v>-0.1798561151079098</v>
       </c>
       <c r="J71" t="n">
+        <v>83245</v>
+      </c>
+      <c r="K71" t="n">
         <v>924431</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1027505056.5</v>
       </c>
       <c r="L71" t="n">
         <v>-0.001798561151079126</v>
@@ -14654,10 +14654,10 @@
         <v>0.4504504504504568</v>
       </c>
       <c r="J72" t="n">
+        <v>77317</v>
+      </c>
+      <c r="K72" t="n">
         <v>860539</v>
-      </c>
-      <c r="K72" t="n">
-        <v>957779907</v>
       </c>
       <c r="L72" t="n">
         <v>0.004504504504504458</v>
@@ -14696,10 +14696,10 @@
         <v>0.1793721973094132</v>
       </c>
       <c r="J73" t="n">
+        <v>71059</v>
+      </c>
+      <c r="K73" t="n">
         <v>792668</v>
-      </c>
-      <c r="K73" t="n">
-        <v>884022987</v>
       </c>
       <c r="L73" t="n">
         <v>0.001793721973094131</v>
@@ -14738,10 +14738,10 @@
         <v>0.7162041181736801</v>
       </c>
       <c r="J74" t="n">
+        <v>85989</v>
+      </c>
+      <c r="K74" t="n">
         <v>963932</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1079121874</v>
       </c>
       <c r="L74" t="n">
         <v>0.0071620411817368</v>
@@ -14780,10 +14780,10 @@
         <v>-1.155555555555563</v>
       </c>
       <c r="J75" t="n">
+        <v>84151</v>
+      </c>
+      <c r="K75" t="n">
         <v>940385</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1051585526.25</v>
       </c>
       <c r="L75" t="n">
         <v>-0.01155555555555565</v>
@@ -14822,10 +14822,10 @@
         <v>-0.6294964028776845</v>
       </c>
       <c r="J76" t="n">
+        <v>75881</v>
+      </c>
+      <c r="K76" t="n">
         <v>840387</v>
-      </c>
-      <c r="K76" t="n">
-        <v>930728602.5</v>
       </c>
       <c r="L76" t="n">
         <v>-0.006294964028776828</v>
@@ -14864,10 +14864,10 @@
         <v>-0.09049773755657523</v>
       </c>
       <c r="J77" t="n">
+        <v>64077</v>
+      </c>
+      <c r="K77" t="n">
         <v>708048</v>
-      </c>
-      <c r="K77" t="n">
-        <v>782747064</v>
       </c>
       <c r="L77" t="n">
         <v>-0.0009049773755657187</v>
@@ -14906,10 +14906,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
+        <v>69849</v>
+      </c>
+      <c r="K78" t="n">
         <v>771129</v>
-      </c>
-      <c r="K78" t="n">
-        <v>850748069.25</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -14948,10 +14948,10 @@
         <v>-2.083333333333321</v>
       </c>
       <c r="J79" t="n">
+        <v>126822</v>
+      </c>
+      <c r="K79" t="n">
         <v>1386160</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1514379800</v>
       </c>
       <c r="L79" t="n">
         <v>-0.02083333333333326</v>
@@ -14990,10 +14990,10 @@
         <v>0.3700277520813982</v>
       </c>
       <c r="J80" t="n">
+        <v>77068</v>
+      </c>
+      <c r="K80" t="n">
         <v>834651</v>
-      </c>
-      <c r="K80" t="n">
-        <v>904344358.5</v>
       </c>
       <c r="L80" t="n">
         <v>0.003700277520813922</v>
@@ -15032,10 +15032,10 @@
         <v>-0.6451612903225833</v>
       </c>
       <c r="J81" t="n">
+        <v>55171</v>
+      </c>
+      <c r="K81" t="n">
         <v>596402</v>
-      </c>
-      <c r="K81" t="n">
-        <v>645008763</v>
       </c>
       <c r="L81" t="n">
         <v>-0.006451612903225823</v>
@@ -15074,10 +15074,10 @@
         <v>1.298701298701304</v>
       </c>
       <c r="J82" t="n">
+        <v>123691</v>
+      </c>
+      <c r="K82" t="n">
         <v>1341430</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1455116192.5</v>
       </c>
       <c r="L82" t="n">
         <v>0.0129870129870131</v>
@@ -15116,10 +15116,10 @@
         <v>-0.549450549450554</v>
       </c>
       <c r="J83" t="n">
+        <v>104693</v>
+      </c>
+      <c r="K83" t="n">
         <v>1139583</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1242715261.5</v>
       </c>
       <c r="L83" t="n">
         <v>-0.005494505494505586</v>
@@ -15158,10 +15158,10 @@
         <v>-0.5524861878452921</v>
       </c>
       <c r="J84" t="n">
+        <v>71500</v>
+      </c>
+      <c r="K84" t="n">
         <v>773276</v>
-      </c>
-      <c r="K84" t="n">
-        <v>836297994</v>
       </c>
       <c r="L84" t="n">
         <v>-0.005524861878452914</v>
@@ -15200,10 +15200,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
+        <v>69777</v>
+      </c>
+      <c r="K85" t="n">
         <v>753239</v>
-      </c>
-      <c r="K85" t="n">
-        <v>812556571.25</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>-0.2777777777777883</v>
       </c>
       <c r="J86" t="n">
+        <v>109041</v>
+      </c>
+      <c r="K86" t="n">
         <v>1176012</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1267740936</v>
       </c>
       <c r="L86" t="n">
         <v>-0.002777777777777879</v>
@@ -15284,10 +15284,10 @@
         <v>-0.2785515320334203</v>
       </c>
       <c r="J87" t="n">
+        <v>77404</v>
+      </c>
+      <c r="K87" t="n">
         <v>832479</v>
-      </c>
-      <c r="K87" t="n">
-        <v>894290565.75</v>
       </c>
       <c r="L87" t="n">
         <v>-0.00278551532033422</v>
@@ -15326,10 +15326,10 @@
         <v>0.5586592178770996</v>
       </c>
       <c r="J88" t="n">
+        <v>97303</v>
+      </c>
+      <c r="K88" t="n">
         <v>1047469</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1126291042.25</v>
       </c>
       <c r="L88" t="n">
         <v>0.005586592178770999</v>
@@ -15368,10 +15368,10 @@
         <v>0.2777777777777719</v>
       </c>
       <c r="J89" t="n">
+        <v>100736</v>
+      </c>
+      <c r="K89" t="n">
         <v>1087948</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1176343775</v>
       </c>
       <c r="L89" t="n">
         <v>0.002777777777777768</v>
@@ -15410,10 +15410,10 @@
         <v>-0.2770083102493016</v>
       </c>
       <c r="J90" t="n">
+        <v>108625</v>
+      </c>
+      <c r="K90" t="n">
         <v>1168802</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1258215353</v>
       </c>
       <c r="L90" t="n">
         <v>-0.002770083102493048</v>
@@ -15452,10 +15452,10 @@
         <v>1.574074074074073</v>
       </c>
       <c r="J91" t="n">
+        <v>169433</v>
+      </c>
+      <c r="K91" t="n">
         <v>1843428</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2005649664</v>
       </c>
       <c r="L91" t="n">
         <v>0.01574074074074083</v>
@@ -15494,10 +15494,10 @@
         <v>0.638103919781208</v>
       </c>
       <c r="J92" t="n">
+        <v>115446</v>
+      </c>
+      <c r="K92" t="n">
         <v>1271061</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1397531569.5</v>
       </c>
       <c r="L92" t="n">
         <v>0.006381039197812077</v>
@@ -15536,10 +15536,10 @@
         <v>1.268115942028991</v>
       </c>
       <c r="J93" t="n">
+        <v>113688</v>
+      </c>
+      <c r="K93" t="n">
         <v>1261937</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1400434585.75</v>
       </c>
       <c r="L93" t="n">
         <v>0.0126811594202898</v>
@@ -15578,10 +15578,10 @@
         <v>-1.252236135957071</v>
       </c>
       <c r="J94" t="n">
+        <v>93748</v>
+      </c>
+      <c r="K94" t="n">
         <v>1039666</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1154549093</v>
       </c>
       <c r="L94" t="n">
         <v>-0.01252236135957074</v>
@@ -15620,10 +15620,10 @@
         <v>0.1811594202898673</v>
       </c>
       <c r="J95" t="n">
+        <v>86173</v>
+      </c>
+      <c r="K95" t="n">
         <v>952641</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1050524862.75</v>
       </c>
       <c r="L95" t="n">
         <v>0.00181159420289867</v>
@@ -15662,10 +15662,10 @@
         <v>0.0904159132007214</v>
       </c>
       <c r="J96" t="n">
+        <v>68853</v>
+      </c>
+      <c r="K96" t="n">
         <v>761165</v>
-      </c>
-      <c r="K96" t="n">
-        <v>842038781.25</v>
       </c>
       <c r="L96" t="n">
         <v>0.0009041591320071429</v>
@@ -15704,10 +15704,10 @@
         <v>0.8130081300812995</v>
       </c>
       <c r="J97" t="n">
+        <v>75108</v>
+      </c>
+      <c r="K97" t="n">
         <v>833703</v>
-      </c>
-      <c r="K97" t="n">
-        <v>925827181.5</v>
       </c>
       <c r="L97" t="n">
         <v>0.008130081300812941</v>
@@ -15746,10 +15746,10 @@
         <v>0.9856630824372709</v>
       </c>
       <c r="J98" t="n">
+        <v>122435</v>
+      </c>
+      <c r="K98" t="n">
         <v>1373112</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1542004776</v>
       </c>
       <c r="L98" t="n">
         <v>0.009856630824372603</v>
@@ -15788,10 +15788,10 @@
         <v>-0.6211180124223628</v>
       </c>
       <c r="J99" t="n">
+        <v>87386</v>
+      </c>
+      <c r="K99" t="n">
         <v>980475</v>
-      </c>
-      <c r="K99" t="n">
-        <v>1101808781.25</v>
       </c>
       <c r="L99" t="n">
         <v>-0.006211180124223614</v>
@@ -15830,10 +15830,10 @@
         <v>-0.3571428571428495</v>
       </c>
       <c r="J100" t="n">
+        <v>110966</v>
+      </c>
+      <c r="K100" t="n">
         <v>1239485</v>
-      </c>
-      <c r="K100" t="n">
-        <v>1384194873.75</v>
       </c>
       <c r="L100" t="n">
         <v>-0.003571428571428448</v>
@@ -15872,10 +15872,10 @@
         <v>-0.4480286738351318</v>
       </c>
       <c r="J101" t="n">
+        <v>73749</v>
+      </c>
+      <c r="K101" t="n">
         <v>821568</v>
-      </c>
-      <c r="K101" t="n">
-        <v>915226752</v>
       </c>
       <c r="L101" t="n">
         <v>-0.004480286738351325</v>
@@ -15914,10 +15914,10 @@
         <v>-0.7200720072007207</v>
       </c>
       <c r="J102" t="n">
+        <v>87322</v>
+      </c>
+      <c r="K102" t="n">
         <v>966214</v>
-      </c>
-      <c r="K102" t="n">
-        <v>1068391130.5</v>
       </c>
       <c r="L102" t="n">
         <v>-0.007200720072007227</v>
@@ -15956,10 +15956,10 @@
         <v>-0.09066183136899172</v>
       </c>
       <c r="J103" t="n">
+        <v>85642</v>
+      </c>
+      <c r="K103" t="n">
         <v>943770</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1041686137.5</v>
       </c>
       <c r="L103" t="n">
         <v>-0.0009066183136898776</v>
@@ -15998,10 +15998,10 @@
         <v>-0.5444646098003514</v>
       </c>
       <c r="J104" t="n">
+        <v>88280</v>
+      </c>
+      <c r="K104" t="n">
         <v>970193</v>
-      </c>
-      <c r="K104" t="n">
-        <v>1066242107</v>
       </c>
       <c r="L104" t="n">
         <v>-0.005444646098003547</v>
@@ -16040,10 +16040,10 @@
         <v>1.003649635036491</v>
       </c>
       <c r="J105" t="n">
+        <v>86379</v>
+      </c>
+      <c r="K105" t="n">
         <v>952326</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1049225170.5</v>
       </c>
       <c r="L105" t="n">
         <v>0.01003649635036497</v>
@@ -16082,10 +16082,10 @@
         <v>1.445347786811203</v>
       </c>
       <c r="J106" t="n">
+        <v>134859</v>
+      </c>
+      <c r="K106" t="n">
         <v>1503007</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1676228556.75</v>
       </c>
       <c r="L106" t="n">
         <v>0.01445347786811202</v>
@@ -16124,10 +16124,10 @@
         <v>-0.623330365093502</v>
       </c>
       <c r="J107" t="n">
+        <v>71007</v>
+      </c>
+      <c r="K107" t="n">
         <v>794926</v>
-      </c>
-      <c r="K107" t="n">
-        <v>889720925.5</v>
       </c>
       <c r="L107" t="n">
         <v>-0.006233303650934996</v>
@@ -16166,10 +16166,10 @@
         <v>-0.08960573476702319</v>
       </c>
       <c r="J108" t="n">
+        <v>68783</v>
+      </c>
+      <c r="K108" t="n">
         <v>766585</v>
-      </c>
-      <c r="K108" t="n">
-        <v>855125567.5</v>
       </c>
       <c r="L108" t="n">
         <v>-0.0008960573476702871</v>
@@ -16208,10 +16208,10 @@
         <v>0.3587443946188264</v>
       </c>
       <c r="J109" t="n">
+        <v>65758</v>
+      </c>
+      <c r="K109" t="n">
         <v>734851</v>
-      </c>
-      <c r="K109" t="n">
-        <v>821379705.25</v>
       </c>
       <c r="L109" t="n">
         <v>0.003587443946188262</v>
@@ -16250,10 +16250,10 @@
         <v>0.7149240393208228</v>
       </c>
       <c r="J110" t="n">
+        <v>73759</v>
+      </c>
+      <c r="K110" t="n">
         <v>827208</v>
-      </c>
-      <c r="K110" t="n">
-        <v>926472960</v>
       </c>
       <c r="L110" t="n">
         <v>0.0071492403932083</v>
@@ -16292,10 +16292,10 @@
         <v>0.3549245785270712</v>
       </c>
       <c r="J111" t="n">
+        <v>78556</v>
+      </c>
+      <c r="K111" t="n">
         <v>886509</v>
-      </c>
-      <c r="K111" t="n">
-        <v>999760524.75</v>
       </c>
       <c r="L111" t="n">
         <v>0.003549245785270605</v>
@@ -16334,10 +16334,10 @@
         <v>0.08841732979663824</v>
       </c>
       <c r="J112" t="n">
+        <v>100735</v>
+      </c>
+      <c r="K112" t="n">
         <v>1141325</v>
-      </c>
-      <c r="K112" t="n">
-        <v>1294833212.5</v>
       </c>
       <c r="L112" t="n">
         <v>0.0008841732979663064</v>
@@ -16376,10 +16376,10 @@
         <v>0.1766784452296782</v>
       </c>
       <c r="J113" t="n">
+        <v>86407</v>
+      </c>
+      <c r="K113" t="n">
         <v>978991</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1106994073.25</v>
       </c>
       <c r="L113" t="n">
         <v>0.001766784452296832</v>
@@ -16418,10 +16418,10 @@
         <v>0.4409171075837806</v>
       </c>
       <c r="J114" t="n">
+        <v>116035</v>
+      </c>
+      <c r="K114" t="n">
         <v>1316995</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1497423315</v>
       </c>
       <c r="L114" t="n">
         <v>0.004409171075837826</v>
@@ -16460,10 +16460,10 @@
         <v>-0.7023705004389822</v>
       </c>
       <c r="J115" t="n">
+        <v>87686</v>
+      </c>
+      <c r="K115" t="n">
         <v>995233</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1128345413.75</v>
       </c>
       <c r="L115" t="n">
         <v>-0.007023705004389869</v>
@@ -16502,10 +16502,10 @@
         <v>-0.7073386383731217</v>
       </c>
       <c r="J116" t="n">
+        <v>59510</v>
+      </c>
+      <c r="K116" t="n">
         <v>670077</v>
-      </c>
-      <c r="K116" t="n">
-        <v>754841740.5</v>
       </c>
       <c r="L116" t="n">
         <v>-0.007073386383731228</v>
@@ -16544,10 +16544,10 @@
         <v>1.86999109528049</v>
       </c>
       <c r="J117" t="n">
+        <v>117828</v>
+      </c>
+      <c r="K117" t="n">
         <v>1334996</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1513217966</v>
       </c>
       <c r="L117" t="n">
         <v>0.01869991095280499</v>
@@ -16586,10 +16586,10 @@
         <v>0.4370629370629432</v>
       </c>
       <c r="J118" t="n">
+        <v>142848</v>
+      </c>
+      <c r="K118" t="n">
         <v>1637040</v>
-      </c>
-      <c r="K118" t="n">
-        <v>1879731180</v>
       </c>
       <c r="L118" t="n">
         <v>0.004370629370629375</v>
@@ -16628,10 +16628,10 @@
         <v>-1.392515230635336</v>
       </c>
       <c r="J119" t="n">
+        <v>128710</v>
+      </c>
+      <c r="K119" t="n">
         <v>1465359</v>
-      </c>
-      <c r="K119" t="n">
-        <v>1670142920.25</v>
       </c>
       <c r="L119" t="n">
         <v>-0.01392515230635338</v>
@@ -16670,10 +16670,10 @@
         <v>-0.7943512797881717</v>
       </c>
       <c r="J120" t="n">
+        <v>98948</v>
+      </c>
+      <c r="K120" t="n">
         <v>1117119</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1262065190.25</v>
       </c>
       <c r="L120" t="n">
         <v>-0.007943512797881747</v>
@@ -16712,10 +16712,10 @@
         <v>1.779359430604976</v>
       </c>
       <c r="J121" t="n">
+        <v>90620</v>
+      </c>
+      <c r="K121" t="n">
         <v>1028081</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1165586833.75</v>
       </c>
       <c r="L121" t="n">
         <v>0.01779359430604965</v>
@@ -16754,10 +16754,10 @@
         <v>-0.9615384615384566</v>
       </c>
       <c r="J122" t="n">
+        <v>72107</v>
+      </c>
+      <c r="K122" t="n">
         <v>821301</v>
-      </c>
-      <c r="K122" t="n">
-        <v>935461839</v>
       </c>
       <c r="L122" t="n">
         <v>-0.009615384615384581</v>
@@ -16796,10 +16796,10 @@
         <v>0.1765225066195902</v>
       </c>
       <c r="J123" t="n">
+        <v>89346</v>
+      </c>
+      <c r="K123" t="n">
         <v>1011847</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1143893033.5</v>
       </c>
       <c r="L123" t="n">
         <v>0.001765225066195919</v>
@@ -16838,10 +16838,10 @@
         <v>-0.8810572687224639</v>
       </c>
       <c r="J124" t="n">
+        <v>78401</v>
+      </c>
+      <c r="K124" t="n">
         <v>884358</v>
-      </c>
-      <c r="K124" t="n">
-        <v>997113645</v>
       </c>
       <c r="L124" t="n">
         <v>-0.008810572687224627</v>
@@ -16880,10 +16880,10 @@
         <v>0.7111111111111118</v>
       </c>
       <c r="J125" t="n">
+        <v>91921</v>
+      </c>
+      <c r="K125" t="n">
         <v>1037323</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1169063021</v>
       </c>
       <c r="L125" t="n">
         <v>0.007111111111111068</v>
@@ -16922,10 +16922,10 @@
         <v>-0.4413062665489913</v>
       </c>
       <c r="J126" t="n">
+        <v>67970</v>
+      </c>
+      <c r="K126" t="n">
         <v>768060</v>
-      </c>
-      <c r="K126" t="n">
-        <v>867907800</v>
       </c>
       <c r="L126" t="n">
         <v>-0.004413062665489909</v>
@@ -16964,10 +16964,10 @@
         <v>-0.7978723404255307</v>
       </c>
       <c r="J127" t="n">
+        <v>84077</v>
+      </c>
+      <c r="K127" t="n">
         <v>944601</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1062439974.75</v>
       </c>
       <c r="L127" t="n">
         <v>-0.007978723404255317</v>
@@ -17006,10 +17006,10 @@
         <v>-0.5361930294906052</v>
       </c>
       <c r="J128" t="n">
+        <v>79399</v>
+      </c>
+      <c r="K128" t="n">
         <v>886090</v>
-      </c>
-      <c r="K128" t="n">
-        <v>988876440</v>
       </c>
       <c r="L128" t="n">
         <v>-0.005361930294906059</v>
@@ -17048,10 +17048,10 @@
         <v>0.3593890386343139</v>
       </c>
       <c r="J129" t="n">
+        <v>79889</v>
+      </c>
+      <c r="K129" t="n">
         <v>890766</v>
-      </c>
-      <c r="K129" t="n">
-        <v>991422558</v>
       </c>
       <c r="L129" t="n">
         <v>0.003593890386343057</v>
@@ -17090,10 +17090,10 @@
         <v>-0.08952551477170803</v>
       </c>
       <c r="J130" t="n">
+        <v>76797</v>
+      </c>
+      <c r="K130" t="n">
         <v>855899</v>
-      </c>
-      <c r="K130" t="n">
-        <v>955397258.75</v>
       </c>
       <c r="L130" t="n">
         <v>-0.0008952551477170445</v>
@@ -17132,10 +17132,10 @@
         <v>-0.8064516129032245</v>
       </c>
       <c r="J131" t="n">
+        <v>66033</v>
+      </c>
+      <c r="K131" t="n">
         <v>733957</v>
-      </c>
-      <c r="K131" t="n">
-        <v>816160184</v>
       </c>
       <c r="L131" t="n">
         <v>-0.008064516129032251</v>
@@ -17174,10 +17174,10 @@
         <v>-0.9033423667569977</v>
       </c>
       <c r="J132" t="n">
+        <v>94700</v>
+      </c>
+      <c r="K132" t="n">
         <v>1044065</v>
-      </c>
-      <c r="K132" t="n">
-        <v>1150559630</v>
       </c>
       <c r="L132" t="n">
         <v>-0.009033423667569984</v>
@@ -17216,10 +17216,10 @@
         <v>0.3646308113035474</v>
       </c>
       <c r="J133" t="n">
+        <v>84115</v>
+      </c>
+      <c r="K133" t="n">
         <v>925261</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1017093154.25</v>
       </c>
       <c r="L133" t="n">
         <v>0.003646308113035568</v>
@@ -17258,10 +17258,10 @@
         <v>-0.1816530426884612</v>
       </c>
       <c r="J134" t="n">
+        <v>108354</v>
+      </c>
+      <c r="K134" t="n">
         <v>1191895</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1311382473.75</v>
       </c>
       <c r="L134" t="n">
         <v>-0.001816530426884566</v>
@@ -17300,10 +17300,10 @@
         <v>1.45586897179254</v>
       </c>
       <c r="J135" t="n">
+        <v>85028</v>
+      </c>
+      <c r="K135" t="n">
         <v>940833</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1041502131</v>
       </c>
       <c r="L135" t="n">
         <v>0.01455868971792551</v>
@@ -17342,10 +17342,10 @@
         <v>-0.2690582959641358</v>
       </c>
       <c r="J136" t="n">
+        <v>58189</v>
+      </c>
+      <c r="K136" t="n">
         <v>647351</v>
-      </c>
-      <c r="K136" t="n">
-        <v>720501663</v>
       </c>
       <c r="L136" t="n">
         <v>-0.002690582959641308</v>
@@ -17384,10 +17384,10 @@
         <v>0.4496402877697906</v>
       </c>
       <c r="J137" t="n">
+        <v>62971</v>
+      </c>
+      <c r="K137" t="n">
         <v>701495</v>
-      </c>
-      <c r="K137" t="n">
-        <v>781465430</v>
       </c>
       <c r="L137" t="n">
         <v>0.004496402877697925</v>
@@ -17426,10 +17426,10 @@
         <v>0.9847806624888042</v>
       </c>
       <c r="J138" t="n">
+        <v>70483</v>
+      </c>
+      <c r="K138" t="n">
         <v>790467</v>
-      </c>
-      <c r="K138" t="n">
-        <v>886113507</v>
       </c>
       <c r="L138" t="n">
         <v>0.009847806624887934</v>
@@ -17468,10 +17468,10 @@
         <v>-0.1773049645390033</v>
       </c>
       <c r="J139" t="n">
+        <v>57691</v>
+      </c>
+      <c r="K139" t="n">
         <v>649886</v>
-      </c>
-      <c r="K139" t="n">
-        <v>731771636</v>
       </c>
       <c r="L139" t="n">
         <v>-0.001773049645390046</v>
@@ -17510,10 +17510,10 @@
         <v>-0.8880994671403165</v>
       </c>
       <c r="J140" t="n">
+        <v>66253</v>
+      </c>
+      <c r="K140" t="n">
         <v>742369</v>
-      </c>
-      <c r="K140" t="n">
-        <v>831638872.25</v>
       </c>
       <c r="L140" t="n">
         <v>-0.008880994671403131</v>
@@ -17552,10 +17552,10 @@
         <v>0.3584229390680927</v>
       </c>
       <c r="J141" t="n">
+        <v>59594</v>
+      </c>
+      <c r="K141" t="n">
         <v>666266</v>
-      </c>
-      <c r="K141" t="n">
-        <v>745218521</v>
       </c>
       <c r="L141" t="n">
         <v>0.003584229390680926</v>
@@ -17594,10 +17594,10 @@
         <v>-0.1785714285714248</v>
       </c>
       <c r="J142" t="n">
+        <v>45172</v>
+      </c>
+      <c r="K142" t="n">
         <v>505244</v>
-      </c>
-      <c r="K142" t="n">
-        <v>564862792</v>
       </c>
       <c r="L142" t="n">
         <v>-0.001785714285714279</v>
@@ -17636,10 +17636,10 @@
         <v>0.1788908765652913</v>
       </c>
       <c r="J143" t="n">
+        <v>48924</v>
+      </c>
+      <c r="K143" t="n">
         <v>547455</v>
-      </c>
-      <c r="K143" t="n">
-        <v>613149600</v>
       </c>
       <c r="L143" t="n">
         <v>0.001788908765652852</v>
@@ -17678,10 +17678,10 @@
         <v>-0.1785714285714248</v>
       </c>
       <c r="J144" t="n">
+        <v>38994</v>
+      </c>
+      <c r="K144" t="n">
         <v>436340</v>
-      </c>
-      <c r="K144" t="n">
-        <v>488482630</v>
       </c>
       <c r="L144" t="n">
         <v>-0.001785714285714279</v>
@@ -17720,10 +17720,10 @@
         <v>0.1788908765652913</v>
       </c>
       <c r="J145" t="n">
+        <v>57935</v>
+      </c>
+      <c r="K145" t="n">
         <v>648295</v>
-      </c>
-      <c r="K145" t="n">
-        <v>725766252.5</v>
       </c>
       <c r="L145" t="n">
         <v>0.001788908765652852</v>
@@ -17762,10 +17762,10 @@
         <v>-0.714285714285715</v>
       </c>
       <c r="J146" t="n">
+        <v>52273</v>
+      </c>
+      <c r="K146" t="n">
         <v>582584</v>
-      </c>
-      <c r="K146" t="n">
-        <v>649289868</v>
       </c>
       <c r="L146" t="n">
         <v>-0.007142857142857117</v>
@@ -17804,10 +17804,10 @@
         <v>-0.6294964028776845</v>
       </c>
       <c r="J147" t="n">
+        <v>53281</v>
+      </c>
+      <c r="K147" t="n">
         <v>590620</v>
-      </c>
-      <c r="K147" t="n">
-        <v>654702270</v>
       </c>
       <c r="L147" t="n">
         <v>-0.006294964028776828</v>
@@ -17846,10 +17846,10 @@
         <v>0.8144796380090484</v>
       </c>
       <c r="J148" t="n">
+        <v>78873</v>
+      </c>
+      <c r="K148" t="n">
         <v>875491</v>
-      </c>
-      <c r="K148" t="n">
-        <v>971795010</v>
       </c>
       <c r="L148" t="n">
         <v>0.008144796380090469</v>
@@ -17888,10 +17888,10 @@
         <v>1.526032315978455</v>
       </c>
       <c r="J149" t="n">
+        <v>116227</v>
+      </c>
+      <c r="K149" t="n">
         <v>1304648</v>
-      </c>
-      <c r="K149" t="n">
-        <v>1464141218</v>
       </c>
       <c r="L149" t="n">
         <v>0.01526032315978454</v>
@@ -17930,10 +17930,10 @@
         <v>-0.2652519893899305</v>
       </c>
       <c r="J150" t="n">
+        <v>85583</v>
+      </c>
+      <c r="K150" t="n">
         <v>966236</v>
-      </c>
-      <c r="K150" t="n">
-        <v>1094262270</v>
       </c>
       <c r="L150" t="n">
         <v>-0.002652519893899252</v>
@@ -17972,10 +17972,10 @@
         <v>-1.152482269503537</v>
       </c>
       <c r="J151" t="n">
+        <v>98091</v>
+      </c>
+      <c r="K151" t="n">
         <v>1100085</v>
-      </c>
-      <c r="K151" t="n">
-        <v>1233470306.25</v>
       </c>
       <c r="L151" t="n">
         <v>-0.01152482269503541</v>
@@ -18014,10 +18014,10 @@
         <v>-0.4484304932735489</v>
       </c>
       <c r="J152" t="n">
+        <v>88315</v>
+      </c>
+      <c r="K152" t="n">
         <v>983390</v>
-      </c>
-      <c r="K152" t="n">
-        <v>1094513070</v>
       </c>
       <c r="L152" t="n">
         <v>-0.004484304932735439</v>
@@ -18056,10 +18056,10 @@
         <v>0.1801801801801763</v>
       </c>
       <c r="J153" t="n">
+        <v>77012</v>
+      </c>
+      <c r="K153" t="n">
         <v>855213</v>
-      </c>
-      <c r="K153" t="n">
-        <v>949286430</v>
       </c>
       <c r="L153" t="n">
         <v>0.001801801801801783</v>
@@ -18098,10 +18098,10 @@
         <v>-0.08992805755395492</v>
       </c>
       <c r="J154" t="n">
+        <v>95505</v>
+      </c>
+      <c r="K154" t="n">
         <v>1061541</v>
-      </c>
-      <c r="K154" t="n">
-        <v>1180698977.25</v>
       </c>
       <c r="L154" t="n">
         <v>-0.0008992805755395628</v>
@@ -18140,10 +18140,10 @@
         <v>-0.9900990099009851</v>
       </c>
       <c r="J155" t="n">
+        <v>115310</v>
+      </c>
+      <c r="K155" t="n">
         <v>1274757</v>
-      </c>
-      <c r="K155" t="n">
-        <v>1408925174.25</v>
       </c>
       <c r="L155" t="n">
         <v>-0.009900990099009799</v>
@@ -18182,10 +18182,10 @@
         <v>-0.454545454545461</v>
       </c>
       <c r="J156" t="n">
+        <v>80745</v>
+      </c>
+      <c r="K156" t="n">
         <v>884960</v>
-      </c>
-      <c r="K156" t="n">
-        <v>970579880</v>
       </c>
       <c r="L156" t="n">
         <v>-0.00454545454545463</v>
@@ -18224,10 +18224,10 @@
         <v>-1.095890410958897</v>
       </c>
       <c r="J157" t="n">
+        <v>102657</v>
+      </c>
+      <c r="K157" t="n">
         <v>1119473</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1219945701.75</v>
       </c>
       <c r="L157" t="n">
         <v>-0.010958904109589</v>
@@ -18266,10 +18266,10 @@
         <v>-0.6463527239150534</v>
       </c>
       <c r="J158" t="n">
+        <v>74686</v>
+      </c>
+      <c r="K158" t="n">
         <v>804741</v>
-      </c>
-      <c r="K158" t="n">
-        <v>868114353.75</v>
       </c>
       <c r="L158" t="n">
         <v>-0.006463527239150557</v>
@@ -18308,10 +18308,10 @@
         <v>0.3717472118959194</v>
       </c>
       <c r="J159" t="n">
+        <v>71640</v>
+      </c>
+      <c r="K159" t="n">
         <v>772276</v>
-      </c>
-      <c r="K159" t="n">
-        <v>833092735</v>
       </c>
       <c r="L159" t="n">
         <v>0.003717472118959231</v>
@@ -18350,10 +18350,10 @@
         <v>-0.8333333333333319</v>
       </c>
       <c r="J160" t="n">
+        <v>83733</v>
+      </c>
+      <c r="K160" t="n">
         <v>900125</v>
-      </c>
-      <c r="K160" t="n">
-        <v>968084437.5</v>
       </c>
       <c r="L160" t="n">
         <v>-0.008333333333333304</v>
@@ -18392,10 +18392,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
+        <v>73635</v>
+      </c>
+      <c r="K161" t="n">
         <v>788635</v>
-      </c>
-      <c r="K161" t="n">
-        <v>845811037.5</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -18434,10 +18434,10 @@
         <v>-0.7469654528478065</v>
       </c>
       <c r="J162" t="n">
+        <v>104029</v>
+      </c>
+      <c r="K162" t="n">
         <v>1109994</v>
-      </c>
-      <c r="K162" t="n">
-        <v>1184641096.5</v>
       </c>
       <c r="L162" t="n">
         <v>-0.007469654528478031</v>
@@ -18476,10 +18476,10 @@
         <v>-0.2822201317027388</v>
       </c>
       <c r="J163" t="n">
+        <v>104265</v>
+      </c>
+      <c r="K163" t="n">
         <v>1106247</v>
-      </c>
-      <c r="K163" t="n">
-        <v>1174834314</v>
       </c>
       <c r="L163" t="n">
         <v>-0.002822201317027373</v>
@@ -18518,10 +18518,10 @@
         <v>-0.1886792452830149</v>
       </c>
       <c r="J164" t="n">
+        <v>84428</v>
+      </c>
+      <c r="K164" t="n">
         <v>894091</v>
-      </c>
-      <c r="K164" t="n">
-        <v>948183505.5</v>
       </c>
       <c r="L164" t="n">
         <v>-0.001886792452830188</v>
@@ -18560,10 +18560,10 @@
         <v>-0.9451795841209797</v>
       </c>
       <c r="J165" t="n">
+        <v>136635</v>
+      </c>
+      <c r="K165" t="n">
         <v>1438766</v>
-      </c>
-      <c r="K165" t="n">
-        <v>1516099672.5</v>
       </c>
       <c r="L165" t="n">
         <v>-0.009451795841209809</v>
@@ -18602,10 +18602,10 @@
         <v>1.145038167938924</v>
       </c>
       <c r="J166" t="n">
+        <v>175806</v>
+      </c>
+      <c r="K166" t="n">
         <v>1852994</v>
-      </c>
-      <c r="K166" t="n">
-        <v>1945643700</v>
       </c>
       <c r="L166" t="n">
         <v>0.01145038167938917</v>
@@ -18644,10 +18644,10 @@
         <v>-1.226415094339613</v>
       </c>
       <c r="J167" t="n">
+        <v>103730</v>
+      </c>
+      <c r="K167" t="n">
         <v>1091755</v>
-      </c>
-      <c r="K167" t="n">
-        <v>1151528586.25</v>
       </c>
       <c r="L167" t="n">
         <v>-0.01226415094339617</v>
@@ -18686,10 +18686,10 @@
         <v>0.2865329512893922</v>
       </c>
       <c r="J168" t="n">
+        <v>116715</v>
+      </c>
+      <c r="K168" t="n">
         <v>1223173</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1286472202.75</v>
       </c>
       <c r="L168" t="n">
         <v>0.002865329512893977</v>
@@ -18728,10 +18728,10 @@
         <v>-0.1904761904761864</v>
       </c>
       <c r="J169" t="n">
+        <v>76785</v>
+      </c>
+      <c r="K169" t="n">
         <v>806628</v>
-      </c>
-      <c r="K169" t="n">
-        <v>846152772</v>
       </c>
       <c r="L169" t="n">
         <v>-0.001904761904761854</v>
@@ -18770,10 +18770,10 @@
         <v>1.240458015267166</v>
       </c>
       <c r="J170" t="n">
+        <v>65916</v>
+      </c>
+      <c r="K170" t="n">
         <v>695415</v>
-      </c>
-      <c r="K170" t="n">
-        <v>733662825</v>
       </c>
       <c r="L170" t="n">
         <v>0.01240458015267176</v>
@@ -18812,10 +18812,10 @@
         <v>1.131008482563629</v>
       </c>
       <c r="J171" t="n">
+        <v>110313</v>
+      </c>
+      <c r="K171" t="n">
         <v>1177591</v>
-      </c>
-      <c r="K171" t="n">
-        <v>1257078392.5</v>
       </c>
       <c r="L171" t="n">
         <v>0.01131008482563622</v>
@@ -18854,10 +18854,10 @@
         <v>-0.37278657968314</v>
       </c>
       <c r="J172" t="n">
+        <v>67979</v>
+      </c>
+      <c r="K172" t="n">
         <v>727710</v>
-      </c>
-      <c r="K172" t="n">
-        <v>779013555</v>
       </c>
       <c r="L172" t="n">
         <v>-0.003727865796831376</v>
@@ -18896,10 +18896,10 @@
         <v>0.1870907390084317</v>
       </c>
       <c r="J173" t="n">
+        <v>57917</v>
+      </c>
+      <c r="K173" t="n">
         <v>619717</v>
-      </c>
-      <c r="K173" t="n">
-        <v>663097190</v>
       </c>
       <c r="L173" t="n">
         <v>0.00187090739008422</v>
@@ -18938,10 +18938,10 @@
         <v>-0.09337068160599031</v>
       </c>
       <c r="J174" t="n">
+        <v>56089</v>
+      </c>
+      <c r="K174" t="n">
         <v>600430</v>
-      </c>
-      <c r="K174" t="n">
-        <v>642610207.5</v>
       </c>
       <c r="L174" t="n">
         <v>-0.0009337068160598649</v>
@@ -18980,10 +18980,10 @@
         <v>0.09345794392524827</v>
       </c>
       <c r="J175" t="n">
+        <v>40265</v>
+      </c>
+      <c r="K175" t="n">
         <v>431041</v>
-      </c>
-      <c r="K175" t="n">
-        <v>461213870</v>
       </c>
       <c r="L175" t="n">
         <v>0.0009345794392525697</v>
@@ -19022,10 +19022,10 @@
         <v>-1.027077497665744</v>
       </c>
       <c r="J176" t="n">
+        <v>63946</v>
+      </c>
+      <c r="K176" t="n">
         <v>681340</v>
-      </c>
-      <c r="K176" t="n">
-        <v>725627100</v>
       </c>
       <c r="L176" t="n">
         <v>-0.0102707749766574</v>
@@ -19064,10 +19064,10 @@
         <v>-0.4716981132075371</v>
       </c>
       <c r="J177" t="n">
+        <v>52487</v>
+      </c>
+      <c r="K177" t="n">
         <v>555047</v>
-      </c>
-      <c r="K177" t="n">
-        <v>587239726</v>
       </c>
       <c r="L177" t="n">
         <v>-0.004716981132075415</v>
@@ -19106,10 +19106,10 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
+        <v>57056</v>
+      </c>
+      <c r="K178" t="n">
         <v>602512</v>
-      </c>
-      <c r="K178" t="n">
-        <v>636102044</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -19148,10 +19148,10 @@
         <v>-0.4739336492891063</v>
       </c>
       <c r="J179" t="n">
+        <v>101010</v>
+      </c>
+      <c r="K179" t="n">
         <v>1063135</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1117886452.5</v>
       </c>
       <c r="L179" t="n">
         <v>-0.004739336492891044</v>
@@ -19190,10 +19190,10 @@
         <v>0.09523809523809321</v>
       </c>
       <c r="J180" t="n">
+        <v>67847</v>
+      </c>
+      <c r="K180" t="n">
         <v>712730</v>
-      </c>
-      <c r="K180" t="n">
-        <v>748366500</v>
       </c>
       <c r="L180" t="n">
         <v>0.0009523809523810378</v>
@@ -19232,10 +19232,10 @@
         <v>0.2854424357754459</v>
       </c>
       <c r="J181" t="n">
+        <v>58197</v>
+      </c>
+      <c r="K181" t="n">
         <v>612228</v>
-      </c>
-      <c r="K181" t="n">
-        <v>644063856</v>
       </c>
       <c r="L181" t="n">
         <v>0.002854424357754404</v>
@@ -19274,10 +19274,10 @@
         <v>-0.4743833017077698</v>
       </c>
       <c r="J182" t="n">
+        <v>79969</v>
+      </c>
+      <c r="K182" t="n">
         <v>838874</v>
-      </c>
-      <c r="K182" t="n">
-        <v>879139952</v>
       </c>
       <c r="L182" t="n">
         <v>-0.004743833017077703</v>
@@ -19316,10 +19316,10 @@
         <v>0.2859866539561426</v>
       </c>
       <c r="J183" t="n">
+        <v>97924</v>
+      </c>
+      <c r="K183" t="n">
         <v>1028695</v>
-      </c>
-      <c r="K183" t="n">
-        <v>1081158445</v>
       </c>
       <c r="L183" t="n">
         <v>0.002859866539561384</v>
@@ -19358,10 +19358,10 @@
         <v>-1.615969581749049</v>
       </c>
       <c r="J184" t="n">
+        <v>104629</v>
+      </c>
+      <c r="K184" t="n">
         <v>1089714</v>
-      </c>
-      <c r="K184" t="n">
-        <v>1133847417</v>
       </c>
       <c r="L184" t="n">
         <v>-0.01615969581749044</v>
@@ -19400,10 +19400,10 @@
         <v>0.9661835748792237</v>
       </c>
       <c r="J185" t="n">
+        <v>68490</v>
+      </c>
+      <c r="K185" t="n">
         <v>712641</v>
-      </c>
-      <c r="K185" t="n">
-        <v>741681120.75</v>
       </c>
       <c r="L185" t="n">
         <v>0.009661835748792313</v>
@@ -19442,10 +19442,10 @@
         <v>0.09569377990432118</v>
       </c>
       <c r="J186" t="n">
+        <v>45649</v>
+      </c>
+      <c r="K186" t="n">
         <v>476577</v>
-      </c>
-      <c r="K186" t="n">
-        <v>497665532.25</v>
       </c>
       <c r="L186" t="n">
         <v>0.000956937799043267</v>
@@ -19484,10 +19484,10 @@
         <v>-0.5736137667304062</v>
       </c>
       <c r="J187" t="n">
+        <v>80258</v>
+      </c>
+      <c r="K187" t="n">
         <v>835892</v>
-      </c>
-      <c r="K187" t="n">
-        <v>870790491</v>
       </c>
       <c r="L187" t="n">
         <v>-0.005736137667304075</v>
@@ -19526,10 +19526,10 @@
         <v>0.4807692307692205</v>
       </c>
       <c r="J188" t="n">
+        <v>75754</v>
+      </c>
+      <c r="K188" t="n">
         <v>790112</v>
-      </c>
-      <c r="K188" t="n">
-        <v>823296704</v>
       </c>
       <c r="L188" t="n">
         <v>0.004807692307692291</v>
@@ -19568,10 +19568,10 @@
         <v>0.7655502392344504</v>
       </c>
       <c r="J189" t="n">
+        <v>68753</v>
+      </c>
+      <c r="K189" t="n">
         <v>720535</v>
-      </c>
-      <c r="K189" t="n">
-        <v>754940546.25</v>
       </c>
       <c r="L189" t="n">
         <v>0.007655502392344582</v>
@@ -19610,10 +19610,10 @@
         <v>0.4748338081671483</v>
       </c>
       <c r="J190" t="n">
+        <v>71589</v>
+      </c>
+      <c r="K190" t="n">
         <v>754906</v>
-      </c>
-      <c r="K190" t="n">
-        <v>796048377</v>
       </c>
       <c r="L190" t="n">
         <v>0.004748338081671521</v>
@@ -19652,10 +19652,10 @@
         <v>-0.09451795841209629</v>
       </c>
       <c r="J191" t="n">
+        <v>79654</v>
+      </c>
+      <c r="K191" t="n">
         <v>841939</v>
-      </c>
-      <c r="K191" t="n">
-        <v>890140007.75</v>
       </c>
       <c r="L191" t="n">
         <v>-0.000945179584120992</v>
@@ -19694,10 +19694,10 @@
         <v>-0.09460737937558927</v>
       </c>
       <c r="J192" t="n">
+        <v>67733</v>
+      </c>
+      <c r="K192" t="n">
         <v>715603</v>
-      </c>
-      <c r="K192" t="n">
-        <v>756034569.5</v>
       </c>
       <c r="L192" t="n">
         <v>-0.0009460737937558861</v>
@@ -19736,10 +19736,10 @@
         <v>1.041666666666661</v>
       </c>
       <c r="J193" t="n">
+        <v>101476</v>
+      </c>
+      <c r="K193" t="n">
         <v>1076657</v>
-      </c>
-      <c r="K193" t="n">
-        <v>1143140569.75</v>
       </c>
       <c r="L193" t="n">
         <v>0.01041666666666652</v>
@@ -19778,10 +19778,10 @@
         <v>-0.6560449859418959</v>
       </c>
       <c r="J194" t="n">
+        <v>74350</v>
+      </c>
+      <c r="K194" t="n">
         <v>791079</v>
-      </c>
-      <c r="K194" t="n">
-        <v>840719207.25</v>
       </c>
       <c r="L194" t="n">
         <v>-0.006560449859418949</v>
@@ -19820,10 +19820,10 @@
         <v>-0.7547169811320762</v>
       </c>
       <c r="J195" t="n">
+        <v>59223</v>
+      </c>
+      <c r="K195" t="n">
         <v>624212</v>
-      </c>
-      <c r="K195" t="n">
-        <v>658387607</v>
       </c>
       <c r="L195" t="n">
         <v>-0.007547169811320753</v>
@@ -19862,10 +19862,10 @@
         <v>-1.04562737642585</v>
       </c>
       <c r="J196" t="n">
+        <v>79740</v>
+      </c>
+      <c r="K196" t="n">
         <v>834083</v>
-      </c>
-      <c r="K196" t="n">
-        <v>873701942.5</v>
       </c>
       <c r="L196" t="n">
         <v>-0.01045627376425851</v>
@@ -19904,10 +19904,10 @@
         <v>-3.073967339097025</v>
       </c>
       <c r="J197" t="n">
+        <v>154835</v>
+      </c>
+      <c r="K197" t="n">
         <v>1580088</v>
-      </c>
-      <c r="K197" t="n">
-        <v>1611689760</v>
       </c>
       <c r="L197" t="n">
         <v>-0.03073967339097028</v>
@@ -19946,10 +19946,10 @@
         <v>4.261645193260652</v>
       </c>
       <c r="J198" t="n">
+        <v>156891</v>
+      </c>
+      <c r="K198" t="n">
         <v>1622251</v>
-      </c>
-      <c r="K198" t="n">
-        <v>1677813096.75</v>
       </c>
       <c r="L198" t="n">
         <v>0.04261645193260644</v>
@@ -19988,10 +19988,10 @@
         <v>0.5703422053231987</v>
       </c>
       <c r="J199" t="n">
+        <v>70562</v>
+      </c>
+      <c r="K199" t="n">
         <v>744780</v>
-      </c>
-      <c r="K199" t="n">
-        <v>784439535</v>
       </c>
       <c r="L199" t="n">
         <v>0.005703422053231932</v>
@@ -20030,10 +20030,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
+        <v>78340</v>
+      </c>
+      <c r="K200" t="n">
         <v>827664</v>
-      </c>
-      <c r="K200" t="n">
-        <v>876496176</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -20072,10 +20072,10 @@
         <v>0.7561436672967871</v>
       </c>
       <c r="J201" t="n">
+        <v>83369</v>
+      </c>
+      <c r="K201" t="n">
         <v>884129</v>
-      </c>
-      <c r="K201" t="n">
-        <v>936513643.25</v>
       </c>
       <c r="L201" t="n">
         <v>0.007561436672967936</v>
@@ -20114,10 +20114,10 @@
         <v>-0.2814258911819827</v>
       </c>
       <c r="J202" t="n">
+        <v>59531</v>
+      </c>
+      <c r="K202" t="n">
         <v>632522</v>
-      </c>
-      <c r="K202" t="n">
-        <v>672370886</v>
       </c>
       <c r="L202" t="n">
         <v>-0.002814258911819856</v>
@@ -20156,10 +20156,10 @@
         <v>0.8466603951081829</v>
       </c>
       <c r="J203" t="n">
+        <v>109042</v>
+      </c>
+      <c r="K203" t="n">
         <v>1164565</v>
-      </c>
-      <c r="K203" t="n">
-        <v>1246375691.25</v>
       </c>
       <c r="L203" t="n">
         <v>0.008466603951081897</v>
@@ -20198,10 +20198,10 @@
         <v>0.6529850746268517</v>
       </c>
       <c r="J204" t="n">
+        <v>85402</v>
+      </c>
+      <c r="K204" t="n">
         <v>918925</v>
-      </c>
-      <c r="K204" t="n">
-        <v>990371418.75</v>
       </c>
       <c r="L204" t="n">
         <v>0.006529850746268551</v>
@@ -20240,10 +20240,10 @@
         <v>1.112140871177025</v>
       </c>
       <c r="J205" t="n">
+        <v>105889</v>
+      </c>
+      <c r="K205" t="n">
         <v>1148895</v>
-      </c>
-      <c r="K205" t="n">
-        <v>1247412746.25</v>
       </c>
       <c r="L205" t="n">
         <v>0.01112140871177014</v>
@@ -20282,10 +20282,10 @@
         <v>-1.374885426214485</v>
       </c>
       <c r="J206" t="n">
+        <v>69904</v>
+      </c>
+      <c r="K206" t="n">
         <v>757757</v>
-      </c>
-      <c r="K206" t="n">
-        <v>820840270.25</v>
       </c>
       <c r="L206" t="n">
         <v>-0.01374885426214489</v>
@@ -20324,10 +20324,10 @@
         <v>-0.836431226765798</v>
       </c>
       <c r="J207" t="n">
+        <v>56739</v>
+      </c>
+      <c r="K207" t="n">
         <v>607955</v>
-      </c>
-      <c r="K207" t="n">
-        <v>650815827.5</v>
       </c>
       <c r="L207" t="n">
         <v>-0.008364312267657992</v>
@@ -20366,10 +20366,10 @@
         <v>1.780693533270848</v>
       </c>
       <c r="J208" t="n">
+        <v>75241</v>
+      </c>
+      <c r="K208" t="n">
         <v>812976</v>
-      </c>
-      <c r="K208" t="n">
-        <v>877201104</v>
       </c>
       <c r="L208" t="n">
         <v>0.01780693533270838</v>
@@ -20408,10 +20408,10 @@
         <v>-1.1049723756906</v>
       </c>
       <c r="J209" t="n">
+        <v>55904</v>
+      </c>
+      <c r="K209" t="n">
         <v>602365</v>
-      </c>
-      <c r="K209" t="n">
-        <v>649198878.75</v>
       </c>
       <c r="L209" t="n">
         <v>-0.01104972375690605</v>
@@ -20450,10 +20450,10 @@
         <v>-0.09310986964618051</v>
       </c>
       <c r="J210" t="n">
+        <v>44811</v>
+      </c>
+      <c r="K210" t="n">
         <v>481047</v>
-      </c>
-      <c r="K210" t="n">
-        <v>516524216.25</v>
       </c>
       <c r="L210" t="n">
         <v>-0.0009310986964617962</v>
@@ -20492,10 +20492,10 @@
         <v>-0.1863932898415617</v>
       </c>
       <c r="J211" t="n">
+        <v>37954</v>
+      </c>
+      <c r="K211" t="n">
         <v>406104</v>
-      </c>
-      <c r="K211" t="n">
-        <v>434531280</v>
       </c>
       <c r="L211" t="n">
         <v>-0.001863932898415577</v>
@@ -20534,10 +20534,10 @@
         <v>0.9337068160597539</v>
       </c>
       <c r="J212" t="n">
+        <v>46111</v>
+      </c>
+      <c r="K212" t="n">
         <v>496151</v>
-      </c>
-      <c r="K212" t="n">
-        <v>533858476</v>
       </c>
       <c r="L212" t="n">
         <v>0.009337068160597539</v>
@@ -20576,10 +20576,10 @@
         <v>0.3700277520813982</v>
       </c>
       <c r="J213" t="n">
+        <v>46553</v>
+      </c>
+      <c r="K213" t="n">
         <v>503938</v>
-      </c>
-      <c r="K213" t="n">
-        <v>545512885</v>
       </c>
       <c r="L213" t="n">
         <v>0.003700277520813922</v>
@@ -20618,10 +20618,10 @@
         <v>-1.105990783410131</v>
       </c>
       <c r="J214" t="n">
+        <v>63135</v>
+      </c>
+      <c r="K214" t="n">
         <v>680915</v>
-      </c>
-      <c r="K214" t="n">
-        <v>734537056.25</v>
       </c>
       <c r="L214" t="n">
         <v>-0.01105990783410127</v>
@@ -20660,10 +20660,10 @@
         <v>-0.7455731593662634</v>
       </c>
       <c r="J215" t="n">
+        <v>67589</v>
+      </c>
+      <c r="K215" t="n">
         <v>722530</v>
-      </c>
-      <c r="K215" t="n">
-        <v>772384570</v>
       </c>
       <c r="L215" t="n">
         <v>-0.00745573159366264</v>
@@ -20702,10 +20702,10 @@
         <v>0.4694835680751073</v>
       </c>
       <c r="J216" t="n">
+        <v>59020</v>
+      </c>
+      <c r="K216" t="n">
         <v>630034</v>
-      </c>
-      <c r="K216" t="n">
-        <v>671931261</v>
       </c>
       <c r="L216" t="n">
         <v>0.004694835680751019</v>
@@ -20744,10 +20744,10 @@
         <v>0.1869158878504799</v>
       </c>
       <c r="J217" t="n">
+        <v>75416</v>
+      </c>
+      <c r="K217" t="n">
         <v>806946</v>
-      </c>
-      <c r="K217" t="n">
-        <v>864844375.5</v>
       </c>
       <c r="L217" t="n">
         <v>0.001869158878504695</v>
@@ -20786,10 +20786,10 @@
         <v>-0.9328358208955356</v>
       </c>
       <c r="J218" t="n">
+        <v>78637</v>
+      </c>
+      <c r="K218" t="n">
         <v>839054</v>
-      </c>
-      <c r="K218" t="n">
-        <v>894851091</v>
       </c>
       <c r="L218" t="n">
         <v>-0.00932835820895539</v>
@@ -20828,10 +20828,10 @@
         <v>0.1883239171374892</v>
       </c>
       <c r="J219" t="n">
+        <v>60966</v>
+      </c>
+      <c r="K219" t="n">
         <v>648067</v>
-      </c>
-      <c r="K219" t="n">
-        <v>688571187.5</v>
       </c>
       <c r="L219" t="n">
         <v>0.001883239171374784</v>
@@ -20870,10 +20870,10 @@
         <v>0</v>
       </c>
       <c r="J220" t="n">
+        <v>54817</v>
+      </c>
+      <c r="K220" t="n">
         <v>582710</v>
-      </c>
-      <c r="K220" t="n">
-        <v>618983697.5</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -20912,10 +20912,10 @@
         <v>3.571428571428562</v>
       </c>
       <c r="J221" t="n">
+        <v>309348</v>
+      </c>
+      <c r="K221" t="n">
         <v>3401276</v>
-      </c>
-      <c r="K221" t="n">
-        <v>3752457747</v>
       </c>
       <c r="L221" t="n">
         <v>0.03571428571428559</v>
@@ -20954,10 +20954,10 @@
         <v>0.7259528130671513</v>
       </c>
       <c r="J222" t="n">
+        <v>151517</v>
+      </c>
+      <c r="K222" t="n">
         <v>1674259</v>
-      </c>
-      <c r="K222" t="n">
-        <v>1848381936</v>
       </c>
       <c r="L222" t="n">
         <v>0.007259528130671544</v>
@@ -20996,10 +20996,10 @@
         <v>0.5405405405405451</v>
       </c>
       <c r="J223" t="n">
+        <v>124015</v>
+      </c>
+      <c r="K223" t="n">
         <v>1378423</v>
-      </c>
-      <c r="K223" t="n">
-        <v>1531427953</v>
       </c>
       <c r="L223" t="n">
         <v>0.00540540540540535</v>
@@ -21038,10 +21038,10 @@
         <v>-0.2688172043010695</v>
       </c>
       <c r="J224" t="n">
+        <v>102312</v>
+      </c>
+      <c r="K224" t="n">
         <v>1139242</v>
-      </c>
-      <c r="K224" t="n">
-        <v>1270539640.5</v>
       </c>
       <c r="L224" t="n">
         <v>-0.00268817204301075</v>
@@ -21080,10 +21080,10 @@
         <v>-1.168014375561552</v>
       </c>
       <c r="J225" t="n">
+        <v>109881</v>
+      </c>
+      <c r="K225" t="n">
         <v>1216388</v>
-      </c>
-      <c r="K225" t="n">
-        <v>1344716934</v>
       </c>
       <c r="L225" t="n">
         <v>-0.01168014375561555</v>
@@ -21122,10 +21122,10 @@
         <v>0.09090909090908897</v>
       </c>
       <c r="J226" t="n">
+        <v>85101</v>
+      </c>
+      <c r="K226" t="n">
         <v>936958</v>
-      </c>
-      <c r="K226" t="n">
-        <v>1030419560.5</v>
       </c>
       <c r="L226" t="n">
         <v>0.0009090909090909705</v>
@@ -21164,10 +21164,10 @@
         <v>-0.6357856494096302</v>
       </c>
       <c r="J227" t="n">
+        <v>72885</v>
+      </c>
+      <c r="K227" t="n">
         <v>798820</v>
-      </c>
-      <c r="K227" t="n">
-        <v>877104360</v>
       </c>
       <c r="L227" t="n">
         <v>-0.006357856494096259</v>
@@ -21206,10 +21206,10 @@
         <v>-0.1828153564899413</v>
       </c>
       <c r="J228" t="n">
+        <v>85297</v>
+      </c>
+      <c r="K228" t="n">
         <v>931865</v>
-      </c>
-      <c r="K228" t="n">
-        <v>1015732850</v>
       </c>
       <c r="L228" t="n">
         <v>-0.001828153564899404</v>
@@ -21248,10 +21248,10 @@
         <v>-0.2747252747252689</v>
       </c>
       <c r="J229" t="n">
+        <v>94364</v>
+      </c>
+      <c r="K229" t="n">
         <v>1029038</v>
-      </c>
-      <c r="K229" t="n">
-        <v>1123194977</v>
       </c>
       <c r="L229" t="n">
         <v>-0.002747252747252737</v>
@@ -21290,10 +21290,10 @@
         <v>-1.010101010101021</v>
       </c>
       <c r="J230" t="n">
+        <v>93952</v>
+      </c>
+      <c r="K230" t="n">
         <v>1017974</v>
-      </c>
-      <c r="K230" t="n">
-        <v>1102974829</v>
       </c>
       <c r="L230" t="n">
         <v>-0.01010101010101017</v>
@@ -21332,10 +21332,10 @@
         <v>-0.8348794063079765</v>
       </c>
       <c r="J231" t="n">
+        <v>73998</v>
+      </c>
+      <c r="K231" t="n">
         <v>794368</v>
-      </c>
-      <c r="K231" t="n">
-        <v>852952640</v>
       </c>
       <c r="L231" t="n">
         <v>-0.008348794063079756</v>
@@ -21374,10 +21374,10 @@
         <v>-0.5612722170252453</v>
       </c>
       <c r="J232" t="n">
+        <v>91439</v>
+      </c>
+      <c r="K232" t="n">
         <v>974742</v>
-      </c>
-      <c r="K232" t="n">
-        <v>1039806028.5</v>
       </c>
       <c r="L232" t="n">
         <v>-0.005612722170252438</v>
@@ -21416,10 +21416,10 @@
         <v>-1.222953904045162</v>
       </c>
       <c r="J233" t="n">
+        <v>81174</v>
+      </c>
+      <c r="K233" t="n">
         <v>856382</v>
-      </c>
-      <c r="K233" t="n">
-        <v>902840723.5</v>
       </c>
       <c r="L233" t="n">
         <v>-0.01222953904045165</v>
@@ -21458,10 +21458,10 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
+        <v>75682</v>
+      </c>
+      <c r="K234" t="n">
         <v>793529</v>
-      </c>
-      <c r="K234" t="n">
-        <v>833205450</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -21500,10 +21500,10 @@
         <v>-0.8571428571428558</v>
       </c>
       <c r="J235" t="n">
+        <v>71510</v>
+      </c>
+      <c r="K235" t="n">
         <v>747632</v>
-      </c>
-      <c r="K235" t="n">
-        <v>781836164</v>
       </c>
       <c r="L235" t="n">
         <v>-0.008571428571428563</v>
@@ -21542,10 +21542,10 @@
         <v>-0.6724303554274763</v>
       </c>
       <c r="J236" t="n">
+        <v>106957</v>
+      </c>
+      <c r="K236" t="n">
         <v>1110211</v>
-      </c>
-      <c r="K236" t="n">
-        <v>1152676570.75</v>
       </c>
       <c r="L236" t="n">
         <v>-0.00672430355427478</v>
@@ -21584,10 +21584,10 @@
         <v>-0.1934235976789127</v>
       </c>
       <c r="J237" t="n">
+        <v>92365</v>
+      </c>
+      <c r="K237" t="n">
         <v>954133</v>
-      </c>
-      <c r="K237" t="n">
-        <v>985619389</v>
       </c>
       <c r="L237" t="n">
         <v>-0.0019342359767891</v>
@@ -21626,10 +21626,10 @@
         <v>0</v>
       </c>
       <c r="J238" t="n">
+        <v>64254</v>
+      </c>
+      <c r="K238" t="n">
         <v>663103</v>
-      </c>
-      <c r="K238" t="n">
-        <v>684985399</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -21668,10 +21668,10 @@
         <v>1.065891472868211</v>
       </c>
       <c r="J239" t="n">
+        <v>80592</v>
+      </c>
+      <c r="K239" t="n">
         <v>837347</v>
-      </c>
-      <c r="K239" t="n">
-        <v>869794196.25</v>
       </c>
       <c r="L239" t="n">
         <v>0.01065891472868219</v>
@@ -21710,10 +21710,10 @@
         <v>-0.2876318312559862</v>
       </c>
       <c r="J240" t="n">
+        <v>80743</v>
+      </c>
+      <c r="K240" t="n">
         <v>839727</v>
-      </c>
-      <c r="K240" t="n">
-        <v>874365738.75</v>
       </c>
       <c r="L240" t="n">
         <v>-0.002876318312559856</v>
@@ -21752,10 +21752,10 @@
         <v>-0.9615384615384581</v>
       </c>
       <c r="J241" t="n">
+        <v>87025</v>
+      </c>
+      <c r="K241" t="n">
         <v>900711</v>
-      </c>
-      <c r="K241" t="n">
-        <v>932235885</v>
       </c>
       <c r="L241" t="n">
         <v>-0.009615384615384581</v>
@@ -21794,10 +21794,10 @@
         <v>2.621359223300967</v>
       </c>
       <c r="J242" t="n">
+        <v>134168</v>
+      </c>
+      <c r="K242" t="n">
         <v>1399368</v>
-      </c>
-      <c r="K242" t="n">
-        <v>1458491298</v>
       </c>
       <c r="L242" t="n">
         <v>0.02621359223300956</v>
@@ -21836,10 +21836,10 @@
         <v>0.5676442762535525</v>
       </c>
       <c r="J243" t="n">
+        <v>90184</v>
+      </c>
+      <c r="K243" t="n">
         <v>954596</v>
-      </c>
-      <c r="K243" t="n">
-        <v>1008292025</v>
       </c>
       <c r="L243" t="n">
         <v>0.005676442762535538</v>
@@ -21878,10 +21878,10 @@
         <v>0.8466603951081829</v>
       </c>
       <c r="J244" t="n">
+        <v>82983</v>
+      </c>
+      <c r="K244" t="n">
         <v>885428</v>
-      </c>
-      <c r="K244" t="n">
-        <v>944308962</v>
       </c>
       <c r="L244" t="n">
         <v>0.008466603951081897</v>
@@ -21920,10 +21920,10 @@
         <v>-0.8395522388059687</v>
       </c>
       <c r="J245" t="n">
+        <v>77490</v>
+      </c>
+      <c r="K245" t="n">
         <v>825272</v>
-      </c>
-      <c r="K245" t="n">
-        <v>878089408</v>
       </c>
       <c r="L245" t="n">
         <v>-0.00839552238805974</v>
@@ -21962,10 +21962,10 @@
         <v>-1.599247412982125</v>
       </c>
       <c r="J246" t="n">
+        <v>82748</v>
+      </c>
+      <c r="K246" t="n">
         <v>869271</v>
-      </c>
-      <c r="K246" t="n">
-        <v>913386503.25</v>
       </c>
       <c r="L246" t="n">
         <v>-0.0159924741298213</v>
@@ -22004,10 +22004,10 @@
         <v>1.529636711281055</v>
       </c>
       <c r="J247" t="n">
+        <v>95164</v>
+      </c>
+      <c r="K247" t="n">
         <v>1003503</v>
-      </c>
-      <c r="K247" t="n">
-        <v>1059448292.25</v>
       </c>
       <c r="L247" t="n">
         <v>0.01529636711281057</v>
@@ -22046,10 +22046,10 @@
         <v>0.4708097928436979</v>
       </c>
       <c r="J248" t="n">
+        <v>102531</v>
+      </c>
+      <c r="K248" t="n">
         <v>1090926</v>
-      </c>
-      <c r="K248" t="n">
-        <v>1162381653</v>
       </c>
       <c r="L248" t="n">
         <v>0.004708097928437072</v>
@@ -22088,10 +22088,10 @@
         <v>0.9372071227741298</v>
       </c>
       <c r="J249" t="n">
+        <v>107346</v>
+      </c>
+      <c r="K249" t="n">
         <v>1149672</v>
-      </c>
-      <c r="K249" t="n">
-        <v>1231586130</v>
       </c>
       <c r="L249" t="n">
         <v>0.009372071227741197</v>
@@ -22130,10 +22130,10 @@
         <v>1.764159702878378</v>
       </c>
       <c r="J250" t="n">
+        <v>142425</v>
+      </c>
+      <c r="K250" t="n">
         <v>1543176</v>
-      </c>
-      <c r="K250" t="n">
-        <v>1673188578</v>
       </c>
       <c r="L250" t="n">
         <v>0.01764159702878376</v>
@@ -22172,10 +22172,10 @@
         <v>-0.1824817518248298</v>
       </c>
       <c r="J251" t="n">
+        <v>105591</v>
+      </c>
+      <c r="K251" t="n">
         <v>1156222</v>
-      </c>
-      <c r="K251" t="n">
-        <v>1266641201</v>
       </c>
       <c r="L251" t="n">
         <v>-0.001824817518248256</v>
@@ -22214,10 +22214,10 @@
         <v>2.742230347349184</v>
       </c>
       <c r="J252" t="n">
+        <v>182766</v>
+      </c>
+      <c r="K252" t="n">
         <v>2032355</v>
-      </c>
-      <c r="K252" t="n">
-        <v>2254389783.75</v>
       </c>
       <c r="L252" t="n">
         <v>0.02742230347349195</v>
@@ -22256,10 +22256,10 @@
         <v>-1.601423487544481</v>
       </c>
       <c r="J253" t="n">
+        <v>138420</v>
+      </c>
+      <c r="K253" t="n">
         <v>1541305</v>
-      </c>
-      <c r="K253" t="n">
-        <v>1713160507.5</v>
       </c>
       <c r="L253" t="n">
         <v>-0.01601423487544484</v>
@@ -22298,10 +22298,10 @@
         <v>-1.084990958408689</v>
       </c>
       <c r="J254" t="n">
+        <v>85740</v>
+      </c>
+      <c r="K254" t="n">
         <v>942708</v>
-      </c>
-      <c r="K254" t="n">
-        <v>1037450154</v>
       </c>
       <c r="L254" t="n">
         <v>-0.01084990958408694</v>
@@ -22340,10 +22340,10 @@
         <v>-1.462522851919563</v>
       </c>
       <c r="J255" t="n">
+        <v>88812</v>
+      </c>
+      <c r="K255" t="n">
         <v>965828</v>
-      </c>
-      <c r="K255" t="n">
-        <v>1050096493</v>
       </c>
       <c r="L255" t="n">
         <v>-0.01462522851919568</v>
@@ -22382,10 +22382,10 @@
         <v>-2.411873840445268</v>
       </c>
       <c r="J256" t="n">
+        <v>134233</v>
+      </c>
+      <c r="K256" t="n">
         <v>1426893</v>
-      </c>
-      <c r="K256" t="n">
-        <v>1517857428.75</v>
       </c>
       <c r="L256" t="n">
         <v>-0.02411873840445267</v>
@@ -22424,10 +22424,10 @@
         <v>1.235741444866927</v>
       </c>
       <c r="J257" t="n">
+        <v>119539</v>
+      </c>
+      <c r="K257" t="n">
         <v>1265317</v>
-      </c>
-      <c r="K257" t="n">
-        <v>1336807410.5</v>
       </c>
       <c r="L257" t="n">
         <v>0.01235741444866933</v>
@@ -22466,10 +22466,10 @@
         <v>0.5633802816901454</v>
       </c>
       <c r="J258" t="n">
+        <v>111480</v>
+      </c>
+      <c r="K258" t="n">
         <v>1190604</v>
-      </c>
-      <c r="K258" t="n">
-        <v>1276922790</v>
       </c>
       <c r="L258" t="n">
         <v>0.005633802816901401</v>
@@ -22508,10 +22508,10 @@
         <v>-1.867413632119524</v>
       </c>
       <c r="J259" t="n">
+        <v>106262</v>
+      </c>
+      <c r="K259" t="n">
         <v>1125841</v>
-      </c>
-      <c r="K259" t="n">
-        <v>1195643142</v>
       </c>
       <c r="L259" t="n">
         <v>-0.01867413632119519</v>
@@ -22550,10 +22550,10 @@
         <v>-0.8563273073263546</v>
       </c>
       <c r="J260" t="n">
+        <v>103782</v>
+      </c>
+      <c r="K260" t="n">
         <v>1083999</v>
-      </c>
-      <c r="K260" t="n">
-        <v>1135217952.75</v>
       </c>
       <c r="L260" t="n">
         <v>-0.008563273073263544</v>
@@ -22592,10 +22592,10 @@
         <v>-1.823416506717845</v>
       </c>
       <c r="J261" t="n">
+        <v>119756</v>
+      </c>
+      <c r="K261" t="n">
         <v>1236482</v>
-      </c>
-      <c r="K261" t="n">
-        <v>1276976785.5</v>
       </c>
       <c r="L261" t="n">
         <v>-0.01823416506717845</v>
@@ -22634,10 +22634,10 @@
         <v>0.09775171065493438</v>
       </c>
       <c r="J262" t="n">
+        <v>109887</v>
+      </c>
+      <c r="K262" t="n">
         <v>1124140</v>
-      </c>
-      <c r="K262" t="n">
-        <v>1146622800</v>
       </c>
       <c r="L262" t="n">
         <v>0.0009775171065493637</v>
@@ -22676,10 +22676,10 @@
         <v>-1.855468749999995</v>
       </c>
       <c r="J263" t="n">
+        <v>109655</v>
+      </c>
+      <c r="K263" t="n">
         <v>1111353</v>
-      </c>
-      <c r="K263" t="n">
-        <v>1126078427.25</v>
       </c>
       <c r="L263" t="n">
         <v>-0.0185546875</v>
@@ -22718,10 +22718,10 @@
         <v>1.094527363184074</v>
       </c>
       <c r="J264" t="n">
+        <v>89747</v>
+      </c>
+      <c r="K264" t="n">
         <v>906890</v>
-      </c>
-      <c r="K264" t="n">
-        <v>915505455</v>
       </c>
       <c r="L264" t="n">
         <v>0.01094527363184072</v>
@@ -22760,10 +22760,10 @@
         <v>1.181102362204717</v>
       </c>
       <c r="J265" t="n">
+        <v>98120</v>
+      </c>
+      <c r="K265" t="n">
         <v>1004749</v>
-      </c>
-      <c r="K265" t="n">
-        <v>1030118912.25</v>
       </c>
       <c r="L265" t="n">
         <v>0.01181102362204722</v>
@@ -22802,10 +22802,10 @@
         <v>0.09727626459143762</v>
       </c>
       <c r="J266" t="n">
+        <v>83900</v>
+      </c>
+      <c r="K266" t="n">
         <v>863327</v>
-      </c>
-      <c r="K266" t="n">
-        <v>888363483</v>
       </c>
       <c r="L266" t="n">
         <v>0.0009727626459143934</v>
